--- a/output/full_scan/batch_seq8_2026-07-09.xlsx
+++ b/output/full_scan/batch_seq8_2026-07-09.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -641,21 +641,21 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>7827</v>
+        <v>8033</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
         <v/>
       </c>
       <c r="D4" s="3" t="n">
-        <v>809.7437443651629</v>
+        <v>824.8453571652155</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -666,16 +666,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>65.52470077848523</v>
+        <v>78.85540083880886</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>19.231311849595</v>
+        <v>35.4841180530745</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.447004151994188</v>
+        <v>0.5845357165215597</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
@@ -684,31 +684,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.3194394379759284</v>
+        <v>8.649891083839314</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>6907</v>
+        <v>7827</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
         <v/>
       </c>
       <c r="D5" s="3" t="n">
-        <v>781.8996874600783</v>
+        <v>809.7437443651629</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>67.78929582445319</v>
+        <v>65.52470077848523</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>36.19445187711887</v>
+        <v>19.231311849595</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.911700715685535</v>
+        <v>1.447004151994188</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0</v>
@@ -737,31 +737,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>4.395017658676792</v>
+        <v>0.3194394379759284</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>7714</v>
+        <v>6907</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
         <v/>
       </c>
       <c r="D6" s="3" t="n">
-        <v>778.5987816818974</v>
+        <v>781.8996874600783</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>172.5</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -772,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>69.25484324696947</v>
+        <v>67.78929582445319</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>31.631591828027</v>
+        <v>36.19445187711887</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.816737525874136</v>
+        <v>1.911700715685535</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -790,31 +790,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>3.024278969283391</v>
+        <v>4.395017658676792</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>7823</v>
+        <v>7714</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
         <v/>
       </c>
       <c r="D7" s="3" t="n">
-        <v>767.4599983145035</v>
+        <v>778.5987816818974</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>88.8</v>
+        <v>172.5</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -825,13 +825,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>61.08241227921307</v>
+        <v>69.25484324696947</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>27.06002914350886</v>
+        <v>31.631591828027</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>4.450305164433895</v>
+        <v>1.816737525874136</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -843,31 +843,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>1.128832326669473</v>
+        <v>3.024278969283391</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>8038</v>
+        <v>7823</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
         <v/>
       </c>
       <c r="D8" s="3" t="n">
-        <v>763.6356955134751</v>
+        <v>767.4599983145035</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>44.4</v>
+        <v>88.8</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -878,16 +878,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>61.19760651486644</v>
+        <v>61.08241227921307</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>15.66978591536018</v>
+        <v>27.06002914350886</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>2.510754684096762</v>
+        <v>4.450305164433895</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>0</v>
@@ -896,31 +896,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.4347863291695374</v>
+        <v>1.128832326669473</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>7786</v>
+        <v>8038</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v/>
       </c>
       <c r="D9" s="3" t="n">
-        <v>754.8795479580339</v>
+        <v>763.6356955134751</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>132.5</v>
+        <v>44.4</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>61.11321579627627</v>
+        <v>61.19760651486644</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>15.96792388548628</v>
+        <v>15.66978591536018</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.96532693441816</v>
+        <v>2.510754684096762</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>0</v>
@@ -949,31 +949,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.6334747859948227</v>
+        <v>0.4347863291695374</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>6949</v>
+        <v>7786</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
         <v/>
       </c>
       <c r="D10" s="3" t="n">
-        <v>693.9710740060193</v>
+        <v>754.8795479580339</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>925</v>
+        <v>132.5</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -984,13 +984,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>62.74291864639969</v>
+        <v>61.11321579627627</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>39.39924410889115</v>
+        <v>15.96792388548628</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.7486178008097591</v>
+        <v>1.96532693441816</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0</v>
@@ -1002,31 +1002,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>3.117365298115004</v>
+        <v>0.6334747859948227</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>8016</v>
+        <v>6949</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v/>
       </c>
       <c r="D11" s="3" t="n">
-        <v>687.4015576888042</v>
+        <v>693.9710740060193</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>363</v>
+        <v>925</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>70.20663148108574</v>
+        <v>62.74291864639969</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>37.3607013914208</v>
+        <v>39.39924410889115</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.045107210948187</v>
+        <v>0.7486178008097591</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1055,31 +1055,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>3.070650749910989</v>
+        <v>3.117365298115004</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>8042</v>
+        <v>8016</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
         <v/>
       </c>
       <c r="D12" s="3" t="n">
-        <v>677.8505839766343</v>
+        <v>687.4015576888042</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>178</v>
+        <v>363</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1090,13 +1090,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>52.14426823637714</v>
+        <v>70.20663148108574</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>26.49938713690022</v>
+        <v>37.3607013914208</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.9603424809690784</v>
+        <v>1.045107210948187</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1108,31 +1108,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>-5.01653945274342</v>
+        <v>3.070650749910989</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>7828</v>
+        <v>8042</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v/>
       </c>
       <c r="D13" s="3" t="n">
-        <v>675.201164112374</v>
+        <v>677.8505839766343</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2115</v>
+        <v>178</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1143,16 +1143,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>56.18091679645224</v>
+        <v>52.14426823637714</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>27.58309559076064</v>
+        <v>26.49938713690022</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.8441680621671966</v>
+        <v>0.9603424809690784</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>0</v>
@@ -1161,31 +1161,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-38.50842032543557</v>
+        <v>-5.01653945274342</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>7715</v>
+        <v>7828</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
         <v/>
       </c>
       <c r="D14" s="3" t="n">
-        <v>665.5990215441725</v>
+        <v>675.201164112374</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>34</v>
+        <v>2115</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1196,16 +1196,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>55.06546424242824</v>
+        <v>56.18091679645224</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>42.26162863727716</v>
+        <v>27.58309559076064</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.1552461919139179</v>
+        <v>0.8441680621671966</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>0</v>
@@ -1214,31 +1214,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>-0.2649374468208083</v>
+        <v>-38.50842032543557</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>8028</v>
+        <v>7715</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
         <v/>
       </c>
       <c r="D15" s="3" t="n">
-        <v>615.4109721051429</v>
+        <v>665.5990215441725</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>312.5</v>
+        <v>34</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1249,16 +1249,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>51.7153387838152</v>
+        <v>55.06546424242824</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>27.79631829369094</v>
+        <v>42.26162863727716</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.5978600481253848</v>
+        <v>0.1552461919139179</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>0</v>
@@ -1267,31 +1267,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>-1.60260020211704</v>
+        <v>-0.2649374468208083</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>6934</v>
+        <v>7795</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
         <v/>
       </c>
       <c r="D16" s="3" t="n">
-        <v>609.3758409205714</v>
+        <v>636.9919342885255</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>79.7</v>
+        <v>552</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1302,13 +1302,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>68.58125344641816</v>
+        <v>58.67200432363374</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>21.59187043825716</v>
+        <v>33.05086858292353</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.581406187884686</v>
+        <v>0.7148782334914953</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0</v>
@@ -1320,31 +1320,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1.476901885420088</v>
+        <v>8.848285734798409</v>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>6957</v>
+        <v>8028</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
         <v/>
       </c>
       <c r="D17" s="3" t="n">
-        <v>609.191210550414</v>
+        <v>615.4109721051429</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>209.5</v>
+        <v>312.5</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1355,13 +1355,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>69.30126033880198</v>
+        <v>51.7153387838152</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>29.23854873753543</v>
+        <v>27.79631829369094</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.5245746775788807</v>
+        <v>0.5978600481253848</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0</v>
@@ -1373,31 +1373,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>1.351053391307271</v>
+        <v>-1.60260020211704</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>8046</v>
+        <v>6934</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
         <v/>
       </c>
       <c r="D18" s="3" t="n">
-        <v>608.1697526601049</v>
+        <v>609.3758409205714</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1215</v>
+        <v>79.7</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1408,13 +1408,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>64.57336860627171</v>
+        <v>68.58125344641816</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>20.92955072064367</v>
+        <v>21.59187043825716</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1.193833158943318</v>
+        <v>2.581406187884686</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
@@ -1426,31 +1426,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>8.95817612606217</v>
+        <v>1.476901885420088</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>6901</v>
+        <v>6957</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
         <v/>
       </c>
       <c r="D19" s="3" t="n">
-        <v>577.7117641994857</v>
+        <v>609.191210550414</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>20.75</v>
+        <v>209.5</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1461,13 +1461,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>72.74408948020684</v>
+        <v>69.30126033880198</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>52.28112432246289</v>
+        <v>29.23854873753543</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.105476464619275</v>
+        <v>0.5245746775788807</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>0</v>
@@ -1479,31 +1479,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>0.2108383210472366</v>
+        <v>1.351053391307271</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>8040</v>
+        <v>8046</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
         <v/>
       </c>
       <c r="D20" s="3" t="n">
-        <v>547.6523807439658</v>
+        <v>608.1697526601049</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>1215</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>43.5094579828708</v>
+        <v>64.57336860627171</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>28.39447573922576</v>
+        <v>20.92955072064367</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.3275478931326354</v>
+        <v>1.193833158943318</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>0</v>
@@ -1532,31 +1532,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-2.171093354876402</v>
+        <v>8.95817612606217</v>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>6996</v>
+        <v>6901</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
         <v/>
       </c>
       <c r="D21" s="3" t="n">
-        <v>541.5447530397114</v>
+        <v>577.7117641994857</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>195</v>
+        <v>20.75</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1567,13 +1567,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>49.82685854855121</v>
+        <v>72.74408948020684</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>22.1885717256241</v>
+        <v>52.28112432246289</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.141106000676572</v>
+        <v>3.105476464619275</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -1585,31 +1585,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-0.1241598297612274</v>
+        <v>0.2108383210472366</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>7712</v>
+        <v>8040</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v/>
       </c>
       <c r="D22" s="3" t="n">
-        <v>527.9048012684668</v>
+        <v>547.6523807439658</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>185</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1620,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>51.6771444763768</v>
+        <v>43.5094579828708</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>36.81085613024945</v>
+        <v>28.39447573922576</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.322575557258217</v>
+        <v>0.3275478931326354</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>0</v>
@@ -1638,31 +1638,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>-1.946015229648076</v>
+        <v>-2.171093354876402</v>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>6928</v>
+        <v>6996</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
         <v/>
       </c>
       <c r="D23" s="3" t="n">
-        <v>520.3564348219513</v>
+        <v>541.5447530397114</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>53.3</v>
+        <v>195</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -1673,13 +1673,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>57.63566193828964</v>
+        <v>49.82685854855121</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>32.03870092849044</v>
+        <v>22.1885717256241</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.4347882539286762</v>
+        <v>1.141106000676572</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>0</v>
@@ -1691,31 +1691,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.3178441434706642</v>
+        <v>-0.1241598297612274</v>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>6870</v>
+        <v>7712</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
         <v/>
       </c>
       <c r="D24" s="3" t="n">
-        <v>518.5352456195039</v>
+        <v>527.9048012684668</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>289</v>
+        <v>185</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -1726,13 +1726,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>54.18808298476414</v>
+        <v>51.6771444763768</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>20.69329590986408</v>
+        <v>36.81085613024945</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.1832728974954264</v>
+        <v>1.322575557258217</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>0</v>
@@ -1744,31 +1744,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>-0.7414892122170986</v>
+        <v>-1.946015229648076</v>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>7631</v>
+        <v>6928</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
         <v/>
       </c>
       <c r="D25" s="3" t="n">
-        <v>517.2470814966381</v>
+        <v>520.3564348219513</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>153.5</v>
+        <v>53.3</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -1779,13 +1779,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>54.87141540744771</v>
+        <v>57.63566193828964</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>17.989769929404</v>
+        <v>32.03870092849044</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.2939073784791414</v>
+        <v>0.4347882539286762</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>0</v>
@@ -1797,31 +1797,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-0.6669902613590128</v>
+        <v>0.3178441434706642</v>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>7717</v>
+        <v>6870</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
         <v/>
       </c>
       <c r="D26" s="3" t="n">
-        <v>512.2429131338725</v>
+        <v>518.5352456195039</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>422.5</v>
+        <v>289</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -1832,13 +1832,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>32.03154027332101</v>
+        <v>54.18808298476414</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>22.98215457332702</v>
+        <v>20.69329590986408</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.2816613219084758</v>
+        <v>0.1832728974954264</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0</v>
@@ -1850,31 +1850,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>0.6582596039140114</v>
+        <v>-0.7414892122170986</v>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>7820</v>
+        <v>7631</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
         <v/>
       </c>
       <c r="D27" s="3" t="n">
-        <v>491.5789239850064</v>
+        <v>517.2470814966381</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>118.5</v>
+        <v>153.5</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -1885,16 +1885,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>46.10819305070903</v>
+        <v>54.87141540744771</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>22.80177844578542</v>
+        <v>17.989769929404</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.3963335266741871</v>
+        <v>0.2939073784791414</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>0</v>
@@ -1903,31 +1903,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.681180173553699</v>
+        <v>-0.6669902613590128</v>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>7402</v>
+        <v>7717</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
         <v/>
       </c>
       <c r="D28" s="3" t="n">
-        <v>487.9599836910082</v>
+        <v>512.2429131338725</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>131</v>
+        <v>422.5</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -1938,13 +1938,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>63.74607055147074</v>
+        <v>32.03154027332101</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>31.87193753783683</v>
+        <v>22.98215457332702</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.895998369100822</v>
+        <v>0.2816613219084758</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
@@ -1956,31 +1956,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>3.251686895137888</v>
+        <v>0.6582596039140114</v>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>6903</v>
+        <v>7820</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
         <v/>
       </c>
       <c r="D29" s="3" t="n">
-        <v>485.3920352556953</v>
+        <v>491.5789239850064</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>394</v>
+        <v>118.5</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -1991,16 +1991,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>51.64959307204315</v>
+        <v>46.10819305070903</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>9.970553276203274</v>
+        <v>22.80177844578542</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.369092394743471</v>
+        <v>0.3963335266741871</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>0</v>
@@ -2009,31 +2009,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.2292449030543601</v>
+        <v>1.681180173553699</v>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, williams_r_recovery, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>8043</v>
+        <v>7402</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
         <v/>
       </c>
       <c r="D30" s="3" t="n">
-        <v>475.7514469076053</v>
+        <v>487.9599836910082</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2044,13 +2044,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>46.70045581548385</v>
+        <v>63.74607055147074</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>26.68826096121668</v>
+        <v>31.87193753783683</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.402376190359628</v>
+        <v>1.895998369100822</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>0</v>
@@ -2062,31 +2062,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-6.202201158621332</v>
+        <v>3.251686895137888</v>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>7722</v>
+        <v>6903</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
         <v/>
       </c>
       <c r="D31" s="3" t="n">
-        <v>468.6481070990786</v>
+        <v>485.3920352556953</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>321.5</v>
+        <v>394</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>53.38049398383918</v>
+        <v>51.64959307204315</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>36.1011350843017</v>
+        <v>9.970553276203274</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.5056569025529711</v>
+        <v>1.369092394743471</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>0</v>
@@ -2115,31 +2115,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.9460120272400658</v>
+        <v>-0.2292449030543601</v>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>7711</v>
+        <v>8043</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
         <v/>
       </c>
       <c r="D32" s="3" t="n">
-        <v>448.168402592468</v>
+        <v>475.7514469076053</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>307.5</v>
+        <v>173</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2150,13 +2150,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>33.58404502206044</v>
+        <v>46.70045581548385</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>23.32559147019301</v>
+        <v>26.68826096121668</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.3173966296746351</v>
+        <v>0.402376190359628</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>0</v>
@@ -2168,31 +2168,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>-2.214144685673077</v>
+        <v>-6.202201158621332</v>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>7822</v>
+        <v>7722</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
         <v/>
       </c>
       <c r="D33" s="3" t="n">
-        <v>437.6172733359099</v>
+        <v>468.6481070990786</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>998</v>
+        <v>321.5</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2203,13 +2203,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>40.0199529474823</v>
+        <v>53.38049398383918</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>16.26313580679561</v>
+        <v>36.1011350843017</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.7077928517050889</v>
+        <v>0.5056569025529711</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -2221,31 +2221,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>-12.29486330497583</v>
+        <v>-0.9460120272400658</v>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>7788</v>
+        <v>7711</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
         <v/>
       </c>
       <c r="D34" s="3" t="n">
-        <v>432.672435547185</v>
+        <v>448.168402592468</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>250.5</v>
+        <v>307.5</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2256,13 +2256,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>53.53384595892499</v>
+        <v>33.58404502206044</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>26.45841623708994</v>
+        <v>23.32559147019301</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.9988080750308184</v>
+        <v>0.3173966296746351</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
@@ -2274,31 +2274,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>-5.200905329629352</v>
+        <v>-2.214144685673077</v>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>7768</v>
+        <v>7822</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
         <v/>
       </c>
       <c r="D35" s="3" t="n">
-        <v>428.5720821620459</v>
+        <v>437.6172733359099</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>350.5</v>
+        <v>998</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>44.9957083040262</v>
+        <v>40.0199529474823</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>19.31495434697918</v>
+        <v>16.26313580679561</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.6078497991618904</v>
+        <v>0.7077928517050889</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
@@ -2327,31 +2327,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0.8039538015915468</v>
+        <v>-12.29486330497583</v>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>6994</v>
+        <v>7788</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
         <v/>
       </c>
       <c r="D36" s="3" t="n">
-        <v>424.0373102792705</v>
+        <v>432.672435547185</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>41.4</v>
+        <v>250.5</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2362,13 +2362,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>30.62919556896838</v>
+        <v>53.53384595892499</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>30.48485012335409</v>
+        <v>26.45841623708994</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.4208315542572432</v>
+        <v>0.9988080750308184</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
@@ -2380,31 +2380,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-0.4510582557092011</v>
+        <v>-5.200905329629352</v>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>7799</v>
+        <v>7768</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
         <v/>
       </c>
       <c r="D37" s="3" t="n">
-        <v>411.7499454937274</v>
+        <v>428.5720821620459</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>435.5</v>
+        <v>350.5</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -2415,13 +2415,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>60.12411492070577</v>
+        <v>44.9957083040262</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>38.59920645160066</v>
+        <v>19.31495434697918</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1.475752415887216</v>
+        <v>0.6078497991618904</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>0</v>
@@ -2433,31 +2433,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.606444189026984</v>
+        <v>0.8039538015915468</v>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>7769</v>
+        <v>6994</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
         <v/>
       </c>
       <c r="D38" s="3" t="n">
-        <v>410.4768811667781</v>
+        <v>424.0373102792705</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>6660</v>
+        <v>41.4</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -2468,13 +2468,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>48.49965907145662</v>
+        <v>30.62919556896838</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>13.94188275482487</v>
+        <v>30.48485012335409</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.9027191715987511</v>
+        <v>0.4208315542572432</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0</v>
@@ -2486,31 +2486,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>-70.43813889080255</v>
+        <v>-0.4510582557092011</v>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>7556</v>
+        <v>7799</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
         <v/>
       </c>
       <c r="D39" s="3" t="n">
-        <v>406.9366800898908</v>
+        <v>411.7499454937274</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>260</v>
+        <v>435.5</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -2521,13 +2521,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>39.45770650695192</v>
+        <v>60.12411492070577</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>13.14064508594869</v>
+        <v>38.59920645160066</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>1.067579958691466</v>
+        <v>1.475752415887216</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
@@ -2539,31 +2539,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>-1.590277413419576</v>
+        <v>4.606444189026984</v>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>7839</v>
+        <v>7769</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
         <v/>
       </c>
       <c r="D40" s="3" t="n">
-        <v>404.8410216222882</v>
+        <v>410.4768811667781</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>45.45</v>
+        <v>6660</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -2574,16 +2574,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>45.77993511999992</v>
+        <v>48.49965907145662</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>10.06476730772729</v>
+        <v>13.94188275482487</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.1375784075508008</v>
+        <v>0.9027191715987511</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>0</v>
@@ -2592,31 +2592,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0.0563979370990299</v>
+        <v>-70.43813889080255</v>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>6944</v>
+        <v>7556</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
         <v/>
       </c>
       <c r="D41" s="3" t="n">
-        <v>403.589446860455</v>
+        <v>406.9366800898908</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>998</v>
+        <v>260</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -2627,13 +2627,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>53.97414305633525</v>
+        <v>39.45770650695192</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>13.542172586815</v>
+        <v>13.14064508594869</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.9308369947680232</v>
+        <v>1.067579958691466</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
@@ -2645,31 +2645,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-6.063096856568521</v>
+        <v>-1.590277413419576</v>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>7760</v>
+        <v>7839</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
         <v/>
       </c>
       <c r="D42" s="3" t="n">
-        <v>403.3388153170852</v>
+        <v>404.8410216222882</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>35.6</v>
+        <v>45.45</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -2680,16 +2680,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>62.59676598387714</v>
+        <v>45.77993511999992</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>37.75336209420588</v>
+        <v>10.06476730772729</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.4409602829869691</v>
+        <v>0.1375784075508008</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>0</v>
@@ -2698,31 +2698,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.3694364965283102</v>
+        <v>0.0563979370990299</v>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>6902</v>
+        <v>6944</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
         <v/>
       </c>
       <c r="D43" s="3" t="n">
-        <v>393.7113474025167</v>
+        <v>403.589446860455</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>137.5</v>
+        <v>998</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -2733,13 +2733,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>55.36736359474741</v>
+        <v>53.97414305633525</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>20.1038135463042</v>
+        <v>13.542172586815</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.2329276147208781</v>
+        <v>0.9308369947680232</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>0</v>
@@ -2751,31 +2751,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>-0.3703481302784628</v>
+        <v>-6.063096856568521</v>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>6962</v>
+        <v>7760</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
         <v/>
       </c>
       <c r="D44" s="3" t="n">
-        <v>391.8013081569786</v>
+        <v>403.3388153170852</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>35.95</v>
+        <v>35.6</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -2786,13 +2786,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>43.01946881248563</v>
+        <v>62.59676598387714</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>12.75971975981366</v>
+        <v>37.75336209420588</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.8047189869958328</v>
+        <v>0.4409602829869691</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
@@ -2804,31 +2804,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>-0.22846100106108</v>
+        <v>0.3694364965283102</v>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>6965</v>
+        <v>8021</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
         <v/>
       </c>
       <c r="D45" s="3" t="n">
-        <v>377.1843931304294</v>
+        <v>399.791263574308</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>80</v>
+        <v>521</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -2839,16 +2839,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>52.20498641665363</v>
+        <v>50.73456019767337</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>22.25081508498936</v>
+        <v>18.85153750921001</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.5680626029119896</v>
+        <v>0.0830479174197899</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>0</v>
@@ -2857,31 +2857,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>0.151930499195473</v>
+        <v>-9.180408037579276</v>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>7818</v>
+        <v>6902</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
         <v/>
       </c>
       <c r="D46" s="3" t="n">
-        <v>375.8985836951426</v>
+        <v>393.7113474025167</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>70.2</v>
+        <v>137.5</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -2892,13 +2892,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>57.27089781392089</v>
+        <v>55.36736359474741</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>32.30769006141823</v>
+        <v>20.1038135463042</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.73327262661435</v>
+        <v>0.2329276147208781</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>0</v>
@@ -2910,31 +2910,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>1.718701480670981</v>
+        <v>-0.3703481302784628</v>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>6916</v>
+        <v>6962</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
         <v/>
       </c>
       <c r="D47" s="3" t="n">
-        <v>373.6132347063673</v>
+        <v>391.8013081569786</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>20.15</v>
+        <v>35.95</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -2945,13 +2945,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>49.45269420064002</v>
+        <v>43.01946881248563</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>18.77870899145417</v>
+        <v>12.75971975981366</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.212716101588165</v>
+        <v>0.8047189869958328</v>
       </c>
       <c r="K47" s="3" t="n">
         <v>0</v>
@@ -2963,31 +2963,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>-0.1541319073358627</v>
+        <v>-0.22846100106108</v>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>7734</v>
+        <v>6965</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
         <v/>
       </c>
       <c r="D48" s="3" t="n">
-        <v>370.4252442852194</v>
+        <v>377.1843931304294</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2835</v>
+        <v>80</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -2998,16 +2998,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>41.81263288769653</v>
+        <v>52.20498641665363</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>15.66271249575039</v>
+        <v>22.25081508498936</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.2576035571302245</v>
+        <v>0.5680626029119896</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -3016,31 +3016,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>-41.22411777236361</v>
+        <v>0.151930499195473</v>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>6890</v>
+        <v>7818</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
         <v/>
       </c>
       <c r="D49" s="3" t="n">
-        <v>370.1476617649608</v>
+        <v>375.8985836951426</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>206</v>
+        <v>70.2</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3051,13 +3051,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>47.04697223665249</v>
+        <v>57.27089781392089</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>18.82476032668959</v>
+        <v>32.30769006141823</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.9427276747293294</v>
+        <v>0.73327262661435</v>
       </c>
       <c r="K49" s="3" t="n">
         <v>0</v>
@@ -3069,31 +3069,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>-4.348860040622803</v>
+        <v>1.718701480670981</v>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>6951</v>
+        <v>6916</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
         <v/>
       </c>
       <c r="D50" s="3" t="n">
-        <v>369.1065317235509</v>
+        <v>373.6132347063673</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>78.7</v>
+        <v>20.15</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3104,13 +3104,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>47.44109772578857</v>
+        <v>49.45269420064002</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>21.92213183334803</v>
+        <v>18.77870899145417</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>1.246109337475753</v>
+        <v>0.212716101588165</v>
       </c>
       <c r="K50" s="3" t="n">
         <v>0</v>
@@ -3122,31 +3122,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>0.1838906480326695</v>
+        <v>-0.1541319073358627</v>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>7805</v>
+        <v>7734</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
         <v/>
       </c>
       <c r="D51" s="3" t="n">
-        <v>367.5951086022051</v>
+        <v>370.4252442852194</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>646</v>
+        <v>2835</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3157,16 +3157,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>34.47307932179889</v>
+        <v>41.81263288769653</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>29.1655688896729</v>
+        <v>15.66271249575039</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.4126267848134433</v>
+        <v>0.2576035571302245</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51" s="3" t="n">
         <v>0</v>
@@ -3175,31 +3175,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-1.624145921567855</v>
+        <v>-41.22411777236361</v>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>6937</v>
+        <v>6890</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
         <v/>
       </c>
       <c r="D52" s="3" t="n">
-        <v>365.7484381391925</v>
+        <v>370.1476617649608</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>258.5</v>
+        <v>206</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -3210,13 +3210,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>41.58821051398383</v>
+        <v>47.04697223665249</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>11.66045155161867</v>
+        <v>18.82476032668959</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.5558910775457436</v>
+        <v>0.9427276747293294</v>
       </c>
       <c r="K52" s="3" t="n">
         <v>0</v>
@@ -3228,31 +3228,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>-0.2642627752994722</v>
+        <v>-4.348860040622803</v>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>6877</v>
+        <v>6951</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
         <v/>
       </c>
       <c r="D53" s="3" t="n">
-        <v>363.3623638600944</v>
+        <v>369.1065317235509</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>132.5</v>
+        <v>78.7</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -3263,16 +3263,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>47.0522230577369</v>
+        <v>47.44109772578857</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>14.81593524135605</v>
+        <v>21.92213183334803</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.305062344974368</v>
+        <v>1.246109337475753</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="3" t="n">
         <v>0</v>
@@ -3281,31 +3281,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>1.002289235337011</v>
+        <v>0.1838906480326695</v>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>7747</v>
+        <v>7805</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
         <v/>
       </c>
       <c r="D54" s="3" t="n">
-        <v>359.7446520819311</v>
+        <v>367.5951086022051</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>129</v>
+        <v>646</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -3316,13 +3316,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>51.7696287667076</v>
+        <v>34.47307932179889</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>4.196623574192596</v>
+        <v>29.1655688896729</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.2290081313536389</v>
+        <v>0.4126267848134433</v>
       </c>
       <c r="K54" s="3" t="n">
         <v>0</v>
@@ -3334,31 +3334,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>-0.1267747151014173</v>
+        <v>-1.624145921567855</v>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>6983</v>
+        <v>6937</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
         <v/>
       </c>
       <c r="D55" s="3" t="n">
-        <v>358.0912332595235</v>
+        <v>365.7484381391925</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>349.5</v>
+        <v>258.5</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -3369,13 +3369,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>44.35696361579516</v>
+        <v>41.58821051398383</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>10.04619420721304</v>
+        <v>11.66045155161867</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.3081349841485361</v>
+        <v>0.5558910775457436</v>
       </c>
       <c r="K55" s="3" t="n">
         <v>0</v>
@@ -3387,31 +3387,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>0.69084471980422</v>
+        <v>-0.2642627752994722</v>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>7753</v>
+        <v>6877</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
         <v/>
       </c>
       <c r="D56" s="3" t="n">
-        <v>347.9967932480413</v>
+        <v>363.3623638600944</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>42.5</v>
+        <v>132.5</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -3422,16 +3422,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>49.18736393459205</v>
+        <v>47.0522230577369</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>25.08255189830742</v>
+        <v>14.81593524135605</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.2660209729607627</v>
+        <v>0.305062344974368</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="3" t="n">
         <v>0</v>
@@ -3440,31 +3440,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.0092456039728378</v>
+        <v>1.002289235337011</v>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>6933</v>
+        <v>7747</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
         <v/>
       </c>
       <c r="D57" s="3" t="n">
-        <v>347.1411986314473</v>
+        <v>359.7446520819311</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>157.5</v>
+        <v>129</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -3475,13 +3475,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>53.73800876383001</v>
+        <v>51.7696287667076</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>18.85947890473542</v>
+        <v>4.196623574192596</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.9511992847274796</v>
+        <v>0.2290081313536389</v>
       </c>
       <c r="K57" s="3" t="n">
         <v>0</v>
@@ -3493,31 +3493,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>1.075909353676821</v>
+        <v>-0.1267747151014173</v>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>7704</v>
+        <v>6983</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
         <v/>
       </c>
       <c r="D58" s="3" t="n">
-        <v>345.9775013456459</v>
+        <v>358.0912332595235</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>60</v>
+        <v>349.5</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -3528,13 +3528,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>43.08052775911585</v>
+        <v>44.35696361579516</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>10.35003663128312</v>
+        <v>10.04619420721304</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.4674774304936214</v>
+        <v>0.3081349841485361</v>
       </c>
       <c r="K58" s="3" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>-0.2137068840730075</v>
+        <v>0.69084471980422</v>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
@@ -3556,21 +3556,21 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>6862</v>
+        <v>7753</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
         <v/>
       </c>
       <c r="D59" s="3" t="n">
-        <v>345.0694609867115</v>
+        <v>347.9967932480413</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>181.5</v>
+        <v>42.5</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -3581,13 +3581,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>44.44859701073885</v>
+        <v>49.18736393459205</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>18.98089112253741</v>
+        <v>25.08255189830742</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.3280607157287171</v>
+        <v>0.2660209729607627</v>
       </c>
       <c r="K59" s="3" t="n">
         <v>0</v>
@@ -3599,31 +3599,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>-2.812789303335976</v>
+        <v>-0.0092456039728378</v>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>7821</v>
+        <v>6933</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
         <v/>
       </c>
       <c r="D60" s="3" t="n">
-        <v>344.9200867577227</v>
+        <v>347.1411986314473</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>41</v>
+        <v>157.5</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -3634,13 +3634,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>34.10662081824589</v>
+        <v>53.73800876383001</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>26.67316484279294</v>
+        <v>18.85947890473542</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.3955972118325168</v>
+        <v>0.9511992847274796</v>
       </c>
       <c r="K60" s="3" t="n">
         <v>0</v>
@@ -3652,31 +3652,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>-0.0368639806390169</v>
+        <v>1.075909353676821</v>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>7792</v>
+        <v>7704</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
         <v/>
       </c>
       <c r="D61" s="3" t="n">
-        <v>342.0459665854466</v>
+        <v>345.9775013456459</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>235.5</v>
+        <v>60</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -3687,13 +3687,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>33.84481343206676</v>
+        <v>43.08052775911585</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>21.04219700946348</v>
+        <v>10.35003663128312</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.4424815915393387</v>
+        <v>0.4674774304936214</v>
       </c>
       <c r="K61" s="3" t="n">
         <v>0</v>
@@ -3705,31 +3705,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>-1.195066357563462</v>
+        <v>-0.2137068840730075</v>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>6869</v>
+        <v>6862</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
         <v/>
       </c>
       <c r="D62" s="3" t="n">
-        <v>326.6636404777527</v>
+        <v>345.0694609867115</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>71.2</v>
+        <v>181.5</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -3740,13 +3740,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>38.86067035849533</v>
+        <v>44.44859701073885</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>26.10419596824365</v>
+        <v>18.98089112253741</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.5619937666619337</v>
+        <v>0.3280607157287171</v>
       </c>
       <c r="K62" s="3" t="n">
         <v>0</v>
@@ -3758,31 +3758,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>0.0380933413092328</v>
+        <v>-2.812789303335976</v>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>7751</v>
+        <v>7821</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
         <v/>
       </c>
       <c r="D63" s="3" t="n">
-        <v>324.4173100399416</v>
+        <v>344.9200867577227</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>1295</v>
+        <v>41</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -3793,13 +3793,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>39.44757101125391</v>
+        <v>34.10662081824589</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>9.860766998789597</v>
+        <v>26.67316484279294</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>1.476844180607912</v>
+        <v>0.3955972118325168</v>
       </c>
       <c r="K63" s="3" t="n">
         <v>0</v>
@@ -3811,31 +3811,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>8.145777822016939</v>
+        <v>-0.0368639806390169</v>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>8047</v>
+        <v>7792</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
         <v/>
       </c>
       <c r="D64" s="3" t="n">
-        <v>322.5700999515211</v>
+        <v>342.0459665854466</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>44</v>
+        <v>235.5</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -3846,16 +3846,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>39.94849771546458</v>
+        <v>33.84481343206676</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>7.110162490525892</v>
+        <v>21.04219700946348</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.8073288779987986</v>
+        <v>0.4424815915393387</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="3" t="n">
         <v>0</v>
@@ -3864,31 +3864,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>-0.5620929104518301</v>
+        <v>-1.195066357563462</v>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>7770</v>
+        <v>6869</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
         <v/>
       </c>
       <c r="D65" s="3" t="n">
-        <v>322.5192228975166</v>
+        <v>326.6636404777527</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>42.6</v>
+        <v>71.2</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -3899,13 +3899,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>49.23205460273553</v>
+        <v>38.86067035849533</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>6.990383331623688</v>
+        <v>26.10419596824365</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.3272373250852448</v>
+        <v>0.5619937666619337</v>
       </c>
       <c r="K65" s="3" t="n">
         <v>0</v>
@@ -3917,31 +3917,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>0.1931446192736043</v>
+        <v>0.0380933413092328</v>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>6919</v>
+        <v>7751</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
         <v/>
       </c>
       <c r="D66" s="3" t="n">
-        <v>322.3901559085514</v>
+        <v>324.4173100399416</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>107.5</v>
+        <v>1295</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -3952,13 +3952,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>56.55356828215206</v>
+        <v>39.44757101125391</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>15.19430829327084</v>
+        <v>9.860766998789597</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.6271624777185797</v>
+        <v>1.476844180607912</v>
       </c>
       <c r="K66" s="3" t="n">
         <v>0</v>
@@ -3970,31 +3970,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>0.7668182504308995</v>
+        <v>8.145777822016939</v>
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>8045</v>
+        <v>8047</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
         <v/>
       </c>
       <c r="D67" s="3" t="n">
-        <v>320.8412753222526</v>
+        <v>322.5700999515211</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>58.4</v>
+        <v>44</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -4005,16 +4005,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>38.28273752446779</v>
+        <v>39.94849771546458</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>11.24634828125999</v>
+        <v>7.110162490525892</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.7578615350408903</v>
+        <v>0.8073288779987986</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="3" t="n">
         <v>0</v>
@@ -4023,31 +4023,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0.1666947708317643</v>
+        <v>-0.5620929104518301</v>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>7732</v>
+        <v>7770</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
         <v/>
       </c>
       <c r="D68" s="3" t="n">
-        <v>317.3498017951256</v>
+        <v>322.5192228975166</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>35.7</v>
+        <v>42.6</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -4058,13 +4058,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>51.77847127471162</v>
+        <v>49.23205460273553</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>10.80537190396174</v>
+        <v>6.990383331623688</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.8896635252108401</v>
+        <v>0.3272373250852448</v>
       </c>
       <c r="K68" s="3" t="n">
         <v>0</v>
@@ -4076,7 +4076,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>1.250389066552851</v>
+        <v>0.1931446192736043</v>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
@@ -4086,21 +4086,21 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>7842</v>
+        <v>6919</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
         <v/>
       </c>
       <c r="D69" s="3" t="n">
-        <v>310.8956004829968</v>
+        <v>322.3901559085514</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>107.5</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -4111,16 +4111,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>39.15241912954303</v>
+        <v>56.55356828215206</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>20.35499744177083</v>
+        <v>15.19430829327084</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.187849824274318</v>
+        <v>0.6271624777185797</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="3" t="n">
         <v>0</v>
@@ -4129,31 +4129,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>0.9166581057404332</v>
+        <v>0.7668182504308995</v>
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>6854</v>
+        <v>8045</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
         <v/>
       </c>
       <c r="D70" s="3" t="n">
-        <v>307.9321804976679</v>
+        <v>320.8412753222526</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>113.5</v>
+        <v>58.4</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -4164,13 +4164,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>29.76518104878899</v>
+        <v>38.28273752446779</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>23.47971782368837</v>
+        <v>11.24634828125999</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>1.527707214277649</v>
+        <v>0.7578615350408903</v>
       </c>
       <c r="K70" s="3" t="n">
         <v>0</v>
@@ -4182,31 +4182,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>-0.1925840120314923</v>
+        <v>0.1666947708317643</v>
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>7547</v>
+        <v>7732</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
         <v/>
       </c>
       <c r="D71" s="3" t="n">
-        <v>303.0944028107281</v>
+        <v>317.3498017951256</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>57.5</v>
+        <v>35.7</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -4217,13 +4217,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>42.33644215435693</v>
+        <v>51.77847127471162</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>11.01890232891943</v>
+        <v>10.80537190396174</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.2890252460727331</v>
+        <v>0.8896635252108401</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>0</v>
@@ -4235,31 +4235,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0.3294211558209008</v>
+        <v>1.250389066552851</v>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>8032</v>
+        <v>7842</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
         <v/>
       </c>
       <c r="D72" s="3" t="n">
-        <v>301.7152547634907</v>
+        <v>310.8956004829968</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>41.8</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -4270,16 +4270,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>41.29813010759938</v>
+        <v>39.15241912954303</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>19.24859753762589</v>
+        <v>20.35499744177083</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.1251730459362888</v>
+        <v>0.187849824274318</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="3" t="n">
         <v>0</v>
@@ -4288,31 +4288,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>-0.4744961203595437</v>
+        <v>0.9166581057404332</v>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>6894</v>
+        <v>6854</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
         <v/>
       </c>
       <c r="D73" s="3" t="n">
-        <v>300.9841177232153</v>
+        <v>307.9321804976679</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>357</v>
+        <v>113.5</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -4323,13 +4323,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>47.69302844355485</v>
+        <v>29.76518104878899</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>18.43937038556122</v>
+        <v>23.47971782368837</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.6597567008758003</v>
+        <v>1.527707214277649</v>
       </c>
       <c r="K73" s="3" t="n">
         <v>0</v>
@@ -4341,31 +4341,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>-1.596144151735394</v>
+        <v>-0.1925840120314923</v>
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>6910</v>
+        <v>7547</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
         <v/>
       </c>
       <c r="D74" s="3" t="n">
-        <v>299.0385828183381</v>
+        <v>303.0944028107281</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>26.9</v>
+        <v>57.5</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -4376,13 +4376,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>38.434805768185</v>
+        <v>42.33644215435693</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>14.1022611280137</v>
+        <v>11.01890232891943</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.1934835548176577</v>
+        <v>0.2890252460727331</v>
       </c>
       <c r="K74" s="3" t="n">
         <v>0</v>
@@ -4394,7 +4394,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>-0.0607415351423135</v>
+        <v>0.3294211558209008</v>
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>6906</v>
+        <v>8032</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
         <v/>
       </c>
       <c r="D75" s="3" t="n">
-        <v>298.577190325238</v>
+        <v>301.7152547634907</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>82</v>
+        <v>41.8</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -4429,13 +4429,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>39.51278552547632</v>
+        <v>41.29813010759938</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>17.85269470492556</v>
+        <v>19.24859753762589</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.3971803849544118</v>
+        <v>0.1251730459362888</v>
       </c>
       <c r="K75" s="3" t="n">
         <v>0</v>
@@ -4447,7 +4447,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>-1.468828732115871</v>
+        <v>-0.4744961203595437</v>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
@@ -4457,21 +4457,21 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>6861</v>
+        <v>6894</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
         <v/>
       </c>
       <c r="D76" s="3" t="n">
-        <v>297.6405097406029</v>
+        <v>300.9841177232153</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>292</v>
+        <v>357</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -4482,13 +4482,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>38.68023829736926</v>
+        <v>47.69302844355485</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>15.251927738751</v>
+        <v>18.43937038556122</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.9615210739241909</v>
+        <v>0.6597567008758003</v>
       </c>
       <c r="K76" s="3" t="n">
         <v>0</v>
@@ -4500,31 +4500,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>-4.007093229929875</v>
+        <v>-1.596144151735394</v>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>7721</v>
+        <v>6910</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
         <v/>
       </c>
       <c r="D77" s="3" t="n">
-        <v>294.8380842922334</v>
+        <v>299.0385828183381</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>71</v>
+        <v>26.9</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -4535,13 +4535,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>44.80168470602754</v>
+        <v>38.434805768185</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>10.93154347321739</v>
+        <v>14.1022611280137</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.1445584497526122</v>
+        <v>0.1934835548176577</v>
       </c>
       <c r="K77" s="3" t="n">
         <v>0</v>
@@ -4553,31 +4553,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>-0.284870906582948</v>
+        <v>-0.0607415351423135</v>
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>6967</v>
+        <v>6906</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
         <v/>
       </c>
       <c r="D78" s="3" t="n">
-        <v>294.6658513074201</v>
+        <v>298.577190325238</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -4588,13 +4588,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>43.26325148767204</v>
+        <v>39.51278552547632</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>12.28915735641211</v>
+        <v>17.85269470492556</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.6501533329938837</v>
+        <v>0.3971803849544118</v>
       </c>
       <c r="K78" s="3" t="n">
         <v>0</v>
@@ -4606,31 +4606,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>-0.127783283846913</v>
+        <v>-1.468828732115871</v>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>6925</v>
+        <v>6861</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
         <v/>
       </c>
       <c r="D79" s="3" t="n">
-        <v>282.8989807421126</v>
+        <v>297.6405097406029</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>59</v>
+        <v>292</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -4641,13 +4641,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>42.40319709318113</v>
+        <v>38.68023829736926</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>12.1279134112373</v>
+        <v>15.251927738751</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0.4344170993652123</v>
+        <v>0.9615210739241909</v>
       </c>
       <c r="K79" s="3" t="n">
         <v>0</v>
@@ -4659,31 +4659,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>-0.3043106045863477</v>
+        <v>-4.007093229929875</v>
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>7744</v>
+        <v>7721</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
         <v/>
       </c>
       <c r="D80" s="3" t="n">
-        <v>282.2739161503841</v>
+        <v>294.8380842922334</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>463</v>
+        <v>71</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -4694,13 +4694,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>46.63510101050643</v>
+        <v>44.80168470602754</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>12.94767389763662</v>
+        <v>10.93154347321739</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.2186238196630761</v>
+        <v>0.1445584497526122</v>
       </c>
       <c r="K80" s="3" t="n">
         <v>0</v>
@@ -4712,31 +4712,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>2.634616973940215</v>
+        <v>-0.284870906582948</v>
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>6955</v>
+        <v>6967</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
         <v/>
       </c>
       <c r="D81" s="3" t="n">
-        <v>281.7396377697044</v>
+        <v>294.6658513074201</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>117</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -4747,13 +4747,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>48.25629286175799</v>
+        <v>43.26325148767204</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>6.781125710882042</v>
+        <v>12.28915735641211</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.7905554136719082</v>
+        <v>0.6501533329938837</v>
       </c>
       <c r="K81" s="3" t="n">
         <v>0</v>
@@ -4765,31 +4765,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>1.324706438554193</v>
+        <v>-0.127783283846913</v>
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>6922</v>
+        <v>6925</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
         <v/>
       </c>
       <c r="D82" s="3" t="n">
-        <v>279.1347464297845</v>
+        <v>282.8989807421126</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>177.5</v>
+        <v>59</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -4800,13 +4800,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>46.04941074481724</v>
+        <v>42.40319709318113</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>16.13593446400723</v>
+        <v>12.1279134112373</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>0.7974892534345547</v>
+        <v>0.4344170993652123</v>
       </c>
       <c r="K82" s="3" t="n">
         <v>0</v>
@@ -4818,31 +4818,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>-0.045783786045431</v>
+        <v>-0.3043106045863477</v>
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>7810</v>
+        <v>7744</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
         <v/>
       </c>
       <c r="D83" s="3" t="n">
-        <v>278.4749999699141</v>
+        <v>282.2739161503841</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>203.5</v>
+        <v>463</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -4853,13 +4853,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>44.60623953240303</v>
+        <v>46.63510101050643</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>12.85548156790139</v>
+        <v>12.94767389763662</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.3707259608305109</v>
+        <v>0.2186238196630761</v>
       </c>
       <c r="K83" s="3" t="n">
         <v>0</v>
@@ -4871,31 +4871,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>1.1532787847772</v>
+        <v>2.634616973940215</v>
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>7750</v>
+        <v>6955</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
         <v/>
       </c>
       <c r="D84" s="3" t="n">
-        <v>268.7650604348559</v>
+        <v>281.7396377697044</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2065</v>
+        <v>117</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -4906,13 +4906,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>44.01945573713492</v>
+        <v>48.25629286175799</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>16.38381558645012</v>
+        <v>6.781125710882042</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.451152216685032</v>
+        <v>0.7905554136719082</v>
       </c>
       <c r="K84" s="3" t="n">
         <v>0</v>
@@ -4924,31 +4924,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>-0.5685854657259384</v>
+        <v>1.324706438554193</v>
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>6924</v>
+        <v>6922</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
         <v/>
       </c>
       <c r="D85" s="3" t="n">
-        <v>265.2868228989308</v>
+        <v>279.1347464297845</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>130</v>
+        <v>177.5</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -4959,13 +4959,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>51.38843575639451</v>
+        <v>46.04941074481724</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>16.82560776944494</v>
+        <v>16.13593446400723</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>1.082274986195472</v>
+        <v>0.7974892534345547</v>
       </c>
       <c r="K85" s="3" t="n">
         <v>0</v>
@@ -4977,31 +4977,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>0.9410839888906848</v>
+        <v>-0.045783786045431</v>
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>6865</v>
+        <v>7810</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
         <v/>
       </c>
       <c r="D86" s="3" t="n">
-        <v>257.4953333203686</v>
+        <v>278.4749999699141</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>0</v>
+        <v>203.5</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -5012,13 +5012,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>20.29159883428026</v>
+        <v>44.60623953240303</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>16.68290481952101</v>
+        <v>12.85548156790139</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.0026063346584309</v>
+        <v>0.3707259608305109</v>
       </c>
       <c r="K86" s="3" t="n">
         <v>0</v>
@@ -5030,31 +5030,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-1.585444712094126</v>
+        <v>1.1532787847772</v>
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>6909</v>
+        <v>7750</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
         <v/>
       </c>
       <c r="D87" s="3" t="n">
-        <v>257.220797738762</v>
+        <v>268.7650604348559</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>51.3</v>
+        <v>2065</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -5065,13 +5065,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>44.84173231119117</v>
+        <v>44.01945573713492</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>16.43522241716726</v>
+        <v>16.38381558645012</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>0.2418643455155242</v>
+        <v>0.451152216685032</v>
       </c>
       <c r="K87" s="3" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>-0.4028328880852014</v>
+        <v>-0.5685854657259384</v>
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
@@ -5093,21 +5093,21 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>7703</v>
+        <v>6924</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
         <v/>
       </c>
       <c r="D88" s="3" t="n">
-        <v>254.7410479256419</v>
+        <v>265.2868228989308</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>201</v>
+        <v>130</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>48.93968834394933</v>
+        <v>51.38843575639451</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>12.56090182699024</v>
+        <v>16.82560776944494</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.8668567750519071</v>
+        <v>1.082274986195472</v>
       </c>
       <c r="K88" s="3" t="n">
         <v>0</v>
@@ -5136,31 +5136,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>-0.5813676697053092</v>
+        <v>0.9410839888906848</v>
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>6971</v>
+        <v>6865</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
         <v/>
       </c>
       <c r="D89" s="3" t="n">
-        <v>248.7964353379251</v>
+        <v>257.4953333203686</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -5171,16 +5171,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>45.75591484800266</v>
+        <v>20.29159883428026</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>18.54081063523489</v>
+        <v>16.68290481952101</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>0.1202245018776939</v>
+        <v>0.0026063346584309</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L89" s="3" t="n">
         <v>0</v>
@@ -5189,31 +5189,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>-0.0453578304074157</v>
+        <v>-1.585444712094126</v>
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>6913</v>
+        <v>6909</v>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
         <v/>
       </c>
       <c r="D90" s="3" t="n">
-        <v>245.0152471991686</v>
+        <v>257.220797738762</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>127</v>
+        <v>51.3</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -5224,16 +5224,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>52.31230306888836</v>
+        <v>44.84173231119117</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>16.36218420593027</v>
+        <v>16.43522241716726</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>1.161087007831343</v>
+        <v>0.2418643455155242</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="3" t="n">
         <v>0</v>
@@ -5242,31 +5242,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>0.9696283402485646</v>
+        <v>-0.4028328880852014</v>
       </c>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>7738</v>
+        <v>7703</v>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
         <v/>
       </c>
       <c r="D91" s="3" t="n">
-        <v>244.7651937397526</v>
+        <v>254.7410479256419</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
@@ -5277,13 +5277,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>46.28673696409531</v>
+        <v>48.93968834394933</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>24.82433780524795</v>
+        <v>12.56090182699024</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.7221987501965099</v>
+        <v>0.8668567750519071</v>
       </c>
       <c r="K91" s="3" t="n">
         <v>0</v>
@@ -5295,31 +5295,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0.2964910515228415</v>
+        <v>-0.5813676697053092</v>
       </c>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>6914</v>
+        <v>6971</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
         <v/>
       </c>
       <c r="D92" s="3" t="n">
-        <v>236.6461908947728</v>
+        <v>248.7964353379251</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>142.5</v>
+        <v>27.3</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -5330,16 +5330,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>46.91513562364692</v>
+        <v>45.75591484800266</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>9.301055134289385</v>
+        <v>18.54081063523489</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.6707749528069579</v>
+        <v>0.1202245018776939</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0</v>
@@ -5348,31 +5348,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0.0678334873940843</v>
+        <v>-0.0453578304074157</v>
       </c>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>6969</v>
+        <v>6913</v>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
         <v/>
       </c>
       <c r="D93" s="3" t="n">
-        <v>234.5131981823239</v>
+        <v>245.0152471991686</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -5383,16 +5383,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>49.76168098852229</v>
+        <v>52.31230306888836</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>26.69739293208618</v>
+        <v>16.36218420593027</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>2.298936639207477</v>
+        <v>1.161087007831343</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="3" t="n">
         <v>0</v>
@@ -5401,31 +5401,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>0.2671758542548029</v>
+        <v>0.9696283402485646</v>
       </c>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>7705</v>
+        <v>7738</v>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
         <v/>
       </c>
       <c r="D94" s="3" t="n">
-        <v>234.1490505963637</v>
+        <v>244.7651937397526</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>30.5</v>
+        <v>168</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>38.10650211372359</v>
+        <v>46.28673696409531</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>19.37888036064569</v>
+        <v>24.82433780524795</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>0.6541152889382036</v>
+        <v>0.7221987501965099</v>
       </c>
       <c r="K94" s="3" t="n">
         <v>0</v>
@@ -5454,31 +5454,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>-0.1454222728159066</v>
+        <v>0.2964910515228415</v>
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>6923</v>
+        <v>6914</v>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
         <v/>
       </c>
       <c r="D95" s="3" t="n">
-        <v>231.468291956123</v>
+        <v>236.6461908947728</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>142.5</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
@@ -5489,13 +5489,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>44.5762690630381</v>
+        <v>46.91513562364692</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>12.67822018993692</v>
+        <v>9.301055134289385</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.8082727665262706</v>
+        <v>0.6707749528069579</v>
       </c>
       <c r="K95" s="3" t="n">
         <v>0</v>
@@ -5507,31 +5507,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>0.2577025327578834</v>
+        <v>0.0678334873940843</v>
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>6863</v>
+        <v>6969</v>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
         <v/>
       </c>
       <c r="D96" s="3" t="n">
-        <v>230.032139291011</v>
+        <v>234.5131981823239</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>92.8</v>
+        <v>26</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
@@ -5542,13 +5542,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>41.40054921894313</v>
+        <v>49.76168098852229</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>20.60221827823517</v>
+        <v>26.69739293208618</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.1941587514346871</v>
+        <v>2.298936639207477</v>
       </c>
       <c r="K96" s="3" t="n">
         <v>0</v>
@@ -5560,31 +5560,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="3" t="n">
-        <v>0.3684407437610368</v>
+        <v>0.2671758542548029</v>
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>6997</v>
+        <v>7705</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
         <v/>
       </c>
       <c r="D97" s="3" t="n">
-        <v>228.0731019285915</v>
+        <v>234.1490505963637</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>30.5</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -5595,13 +5595,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>50.87374335948735</v>
+        <v>38.10650211372359</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>7.644666211466003</v>
+        <v>19.37888036064569</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>0.2204182140318915</v>
+        <v>0.6541152889382036</v>
       </c>
       <c r="K97" s="3" t="n">
         <v>0</v>
@@ -5613,31 +5613,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="3" t="n">
-        <v>-0.0341900829681829</v>
+        <v>-0.1454222728159066</v>
       </c>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>6899</v>
+        <v>6923</v>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
         <v/>
       </c>
       <c r="D98" s="3" t="n">
-        <v>218.6683684623978</v>
+        <v>231.468291956123</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>54.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -5648,13 +5648,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>34.04625831253537</v>
+        <v>44.5762690630381</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>14.93820479783654</v>
+        <v>12.67822018993692</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>0.9242118449439766</v>
+        <v>0.8082727665262706</v>
       </c>
       <c r="K98" s="3" t="n">
         <v>0</v>
@@ -5666,31 +5666,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>-0.3323764674530496</v>
+        <v>0.2577025327578834</v>
       </c>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>7765</v>
+        <v>6863</v>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
         <v/>
       </c>
       <c r="D99" s="3" t="n">
-        <v>216.3177662010121</v>
+        <v>230.032139291011</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>221.5</v>
+        <v>92.8</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -5701,13 +5701,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>38.25188509457006</v>
+        <v>41.40054921894313</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>20.95841079889</v>
+        <v>20.60221827823517</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.4169676386477593</v>
+        <v>0.1941587514346871</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>0</v>
@@ -5719,7 +5719,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>-0.242573900333217</v>
+        <v>0.3684407437610368</v>
       </c>
       <c r="O99" s="3" t="inlineStr">
         <is>
@@ -5729,21 +5729,21 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>7749</v>
+        <v>6997</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
         <v/>
       </c>
       <c r="D100" s="3" t="n">
-        <v>216.15866189966</v>
+        <v>228.0731019285915</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>404</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -5754,13 +5754,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>34.08472250739553</v>
+        <v>50.87374335948735</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>15.49490569347116</v>
+        <v>7.644666211466003</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.2834734020563929</v>
+        <v>0.2204182140318915</v>
       </c>
       <c r="K100" s="3" t="n">
         <v>0</v>
@@ -5772,31 +5772,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>-4.924311626850146</v>
+        <v>-0.0341900829681829</v>
       </c>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>8044</v>
+        <v>6899</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
         <v/>
       </c>
       <c r="D101" s="3" t="n">
-        <v>214.1764594044797</v>
+        <v>218.6683684623978</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>26.8</v>
+        <v>54.7</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -5807,13 +5807,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>41.52098264536683</v>
+        <v>34.04625831253537</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>14.18891212162057</v>
+        <v>14.93820479783654</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0.2486213192443414</v>
+        <v>0.9242118449439766</v>
       </c>
       <c r="K101" s="3" t="n">
         <v>0</v>
@@ -5825,31 +5825,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>-0.3977575224055342</v>
+        <v>-0.3323764674530496</v>
       </c>
       <c r="O101" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>6887</v>
+        <v>7765</v>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
         <v/>
       </c>
       <c r="D102" s="3" t="n">
-        <v>213.9710633676277</v>
+        <v>216.3177662010121</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>33.8</v>
+        <v>221.5</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -5860,13 +5860,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>45.48886166105071</v>
+        <v>38.25188509457006</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>5.139339256830514</v>
+        <v>20.95841079889</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>0.6399454679385927</v>
+        <v>0.4169676386477593</v>
       </c>
       <c r="K102" s="3" t="n">
         <v>0</v>
@@ -5878,31 +5878,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>-0.1638936679619918</v>
+        <v>-0.242573900333217</v>
       </c>
       <c r="O102" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>7730</v>
+        <v>7749</v>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
         <v/>
       </c>
       <c r="D103" s="3" t="n">
-        <v>209.1135777707526</v>
+        <v>216.15866189966</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>183</v>
+        <v>404</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
@@ -5913,13 +5913,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>47.84907316049126</v>
+        <v>34.08472250739553</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>10.27348696853355</v>
+        <v>15.49490569347116</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0.9215102340619056</v>
+        <v>0.2834734020563929</v>
       </c>
       <c r="K103" s="3" t="n">
         <v>0</v>
@@ -5931,31 +5931,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0.4485259988977426</v>
+        <v>-4.924311626850146</v>
       </c>
       <c r="O103" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>6953</v>
+        <v>8044</v>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
         <v/>
       </c>
       <c r="D104" s="3" t="n">
-        <v>202.7766110895432</v>
+        <v>214.1764594044797</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>228</v>
+        <v>26.8</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -5966,13 +5966,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>43.79332016008481</v>
+        <v>41.52098264536683</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>12.77746572420149</v>
+        <v>14.18891212162057</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.3861295447556247</v>
+        <v>0.2486213192443414</v>
       </c>
       <c r="K104" s="3" t="n">
         <v>0</v>
@@ -5984,31 +5984,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="3" t="n">
-        <v>0.2059930995085945</v>
+        <v>-0.3977575224055342</v>
       </c>
       <c r="O104" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>6859</v>
+        <v>6887</v>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
         <v/>
       </c>
       <c r="D105" s="3" t="n">
-        <v>202.463779357938</v>
+        <v>213.9710633676277</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>120.5</v>
+        <v>33.8</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
@@ -6019,13 +6019,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>42.9652950604135</v>
+        <v>45.48886166105071</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>15.945217596882</v>
+        <v>5.139339256830514</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>0.1066902570738212</v>
+        <v>0.6399454679385927</v>
       </c>
       <c r="K105" s="3" t="n">
         <v>0</v>
@@ -6037,31 +6037,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="3" t="n">
-        <v>-1.061681769484795</v>
+        <v>-0.1638936679619918</v>
       </c>
       <c r="O105" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>6936</v>
+        <v>7730</v>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
         <v/>
       </c>
       <c r="D106" s="3" t="n">
-        <v>200.5870156353574</v>
+        <v>209.1135777707526</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>32.65</v>
+        <v>183</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -6072,13 +6072,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>42.20126502218261</v>
+        <v>47.84907316049126</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>13.17221901794784</v>
+        <v>10.27348696853355</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>4.046462224784912</v>
+        <v>0.9215102340619056</v>
       </c>
       <c r="K106" s="3" t="n">
         <v>0</v>
@@ -6090,31 +6090,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.0428852394142012</v>
+        <v>0.4485259988977426</v>
       </c>
       <c r="O106" s="3" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>6855</v>
+        <v>6953</v>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
         <v/>
       </c>
       <c r="D107" s="3" t="n">
-        <v>197.4605930448236</v>
+        <v>202.7766110895432</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>122</v>
+        <v>228</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -6125,13 +6125,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>52.29651936967685</v>
+        <v>43.79332016008481</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>8.041145369677951</v>
+        <v>12.77746572420149</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0.6924604135392959</v>
+        <v>0.3861295447556247</v>
       </c>
       <c r="K107" s="3" t="n">
         <v>0</v>
@@ -6143,31 +6143,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0.4306449897770426</v>
+        <v>0.2059930995085945</v>
       </c>
       <c r="O107" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>7728</v>
+        <v>6859</v>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
         <v/>
       </c>
       <c r="D108" s="3" t="n">
-        <v>192.3704498635812</v>
+        <v>202.463779357938</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>654</v>
+        <v>120.5</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
@@ -6178,16 +6178,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>42.17218318976831</v>
+        <v>42.9652950604135</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>11.8805873631551</v>
+        <v>15.945217596882</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>0.2558557370213209</v>
+        <v>0.1066902570738212</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="3" t="n">
         <v>0</v>
@@ -6196,31 +6196,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="3" t="n">
-        <v>-2.451909477888613</v>
+        <v>-1.061681769484795</v>
       </c>
       <c r="O108" s="3" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>6873</v>
+        <v>6936</v>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
         <v/>
       </c>
       <c r="D109" s="3" t="n">
-        <v>185.1231478298612</v>
+        <v>200.5870156353574</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>32.65</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
@@ -6231,13 +6231,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>52.889836719929</v>
+        <v>42.20126502218261</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>15.53961604921723</v>
+        <v>13.17221901794784</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>0.569297001249601</v>
+        <v>4.046462224784912</v>
       </c>
       <c r="K109" s="3" t="n">
         <v>0</v>
@@ -6249,31 +6249,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="3" t="n">
-        <v>1.068271818973007</v>
+        <v>0.0428852394142012</v>
       </c>
       <c r="O109" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>8034</v>
+        <v>6855</v>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
         <v/>
       </c>
       <c r="D110" s="3" t="n">
-        <v>184.6563415290621</v>
+        <v>197.4605930448236</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>21.15</v>
+        <v>122</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -6284,13 +6284,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>28.34459066516009</v>
+        <v>52.29651936967685</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>23.66825328083181</v>
+        <v>8.041145369677951</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0.508731584636699</v>
+        <v>0.6924604135392959</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -6302,31 +6302,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>-0.1070283566265701</v>
+        <v>0.4306449897770426</v>
       </c>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>7772</v>
+        <v>7728</v>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
         <v/>
       </c>
       <c r="D111" s="3" t="n">
-        <v>169.5077913859875</v>
+        <v>192.3704498635812</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>121.5</v>
+        <v>654</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
@@ -6337,16 +6337,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>37.45182363183303</v>
+        <v>42.17218318976831</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>8.720554023055477</v>
+        <v>11.8805873631551</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0.4677433686825033</v>
+        <v>0.2558557370213209</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -6355,7 +6355,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>-0.2469444029466068</v>
+        <v>-2.451909477888613</v>
       </c>
       <c r="O111" s="3" t="inlineStr">
         <is>
@@ -6365,21 +6365,21 @@
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>7780</v>
+        <v>6873</v>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
         <v/>
       </c>
       <c r="D112" s="3" t="n">
-        <v>167.6784704514292</v>
+        <v>185.1231478298612</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>17.9</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
@@ -6390,13 +6390,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>42.18652842155965</v>
+        <v>52.889836719929</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>14.83674349657514</v>
+        <v>15.53961604921723</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0.6134645911181567</v>
+        <v>0.569297001249601</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -6408,31 +6408,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>-0.0182688263466296</v>
+        <v>1.068271818973007</v>
       </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>6952</v>
+        <v>8034</v>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
         <v/>
       </c>
       <c r="D113" s="3" t="n">
-        <v>166.4539942058721</v>
+        <v>184.6563415290621</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>35.2</v>
+        <v>21.15</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -6443,13 +6443,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>34.61315597549314</v>
+        <v>28.34459066516009</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>17.59526342057275</v>
+        <v>23.66825328083181</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>0.8598002347253284</v>
+        <v>0.508731584636699</v>
       </c>
       <c r="K113" s="3" t="n">
         <v>0</v>
@@ -6461,31 +6461,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>-0.01536787894147</v>
+        <v>-0.1070283566265701</v>
       </c>
       <c r="O113" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>7736</v>
+        <v>7772</v>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
         <v/>
       </c>
       <c r="D114" s="3" t="n">
-        <v>164.467327106767</v>
+        <v>169.5077913859875</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>121.5</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -6496,13 +6496,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>41.22229874460208</v>
+        <v>37.45182363183303</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>13.28760285793871</v>
+        <v>8.720554023055477</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0.8334829319487406</v>
+        <v>0.4677433686825033</v>
       </c>
       <c r="K114" s="3" t="n">
         <v>0</v>
@@ -6514,31 +6514,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0.0114340746977891</v>
+        <v>-0.2469444029466068</v>
       </c>
       <c r="O114" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>8011</v>
+        <v>7780</v>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
         <v/>
       </c>
       <c r="D115" s="3" t="n">
-        <v>163.025846366011</v>
+        <v>167.6784704514292</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -6549,13 +6549,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>44.42195089394784</v>
+        <v>42.18652842155965</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>14.30558486974988</v>
+        <v>14.83674349657514</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>1.292398102679002</v>
+        <v>0.6134645911181567</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -6567,31 +6567,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0.0449982245719742</v>
+        <v>-0.0182688263466296</v>
       </c>
       <c r="O115" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>6918</v>
+        <v>6952</v>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
         <v/>
       </c>
       <c r="D116" s="3" t="n">
-        <v>157.0850751975526</v>
+        <v>166.4539942058721</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>35.2</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
@@ -6602,13 +6602,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>52.23885072811661</v>
+        <v>34.61315597549314</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>13.4830962017074</v>
+        <v>17.59526342057275</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0.4409605856337868</v>
+        <v>0.8598002347253284</v>
       </c>
       <c r="K116" s="3" t="n">
         <v>0</v>
@@ -6620,7 +6620,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0.1896822961665943</v>
+        <v>-0.01536787894147</v>
       </c>
       <c r="O116" s="3" t="inlineStr">
         <is>
@@ -6630,21 +6630,21 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>6931</v>
+        <v>7736</v>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
         <v/>
       </c>
       <c r="D117" s="3" t="n">
-        <v>156.6313441542502</v>
+        <v>164.467327106767</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>39.75</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -6655,13 +6655,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>40.62086944048821</v>
+        <v>41.22229874460208</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>17.35038396306931</v>
+        <v>13.28760285793871</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>0.5679778257363548</v>
+        <v>0.8334829319487406</v>
       </c>
       <c r="K117" s="3" t="n">
         <v>0</v>
@@ -6673,7 +6673,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>0.0689822215103861</v>
+        <v>0.0114340746977891</v>
       </c>
       <c r="O117" s="3" t="inlineStr">
         <is>
@@ -6683,21 +6683,21 @@
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>7740</v>
+        <v>8011</v>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
         <v/>
       </c>
       <c r="D118" s="3" t="n">
-        <v>132.9738466243005</v>
+        <v>163.025846366011</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>147.5</v>
+        <v>17.5</v>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
@@ -6708,13 +6708,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>40.20243559783412</v>
+        <v>44.42195089394784</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>19.02230140622725</v>
+        <v>14.30558486974988</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.5163316295136018</v>
+        <v>1.292398102679002</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0</v>
@@ -6726,31 +6726,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>-0.2294428512641397</v>
+        <v>0.0449982245719742</v>
       </c>
       <c r="O118" s="3" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>7803</v>
+        <v>6918</v>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
         <v/>
       </c>
       <c r="D119" s="3" t="n">
-        <v>125.7876630074972</v>
+        <v>157.0850751975526</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>22.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
@@ -6761,13 +6761,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>42.49598584445019</v>
+        <v>52.23885072811661</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>14.08288007446366</v>
+        <v>13.4830962017074</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>0.6736748085727162</v>
+        <v>0.4409605856337868</v>
       </c>
       <c r="K119" s="3" t="n">
         <v>0</v>
@@ -6779,7 +6779,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="3" t="n">
-        <v>0.188236955834315</v>
+        <v>0.1896822961665943</v>
       </c>
       <c r="O119" s="3" t="inlineStr">
         <is>
@@ -6789,21 +6789,21 @@
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>6988</v>
+        <v>6931</v>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
         <v/>
       </c>
       <c r="D120" s="3" t="n">
-        <v>118.3285876328881</v>
+        <v>156.6313441542502</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>13.6</v>
+        <v>39.75</v>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
@@ -6814,13 +6814,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>38.51959458816293</v>
+        <v>40.62086944048821</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>12.85521732756108</v>
+        <v>17.35038396306931</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0.8896812983225151</v>
+        <v>0.5679778257363548</v>
       </c>
       <c r="K120" s="3" t="n">
         <v>0</v>
@@ -6832,7 +6832,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>0.0530954262412654</v>
+        <v>0.0689822215103861</v>
       </c>
       <c r="O120" s="3" t="inlineStr">
         <is>
@@ -6842,21 +6842,21 @@
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>6895</v>
+        <v>7740</v>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
         <v/>
       </c>
       <c r="D121" s="3" t="n">
-        <v>108.2004780325014</v>
+        <v>132.9738466243005</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>138</v>
+        <v>147.5</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -6867,16 +6867,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>34.33605711600157</v>
+        <v>40.20243559783412</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>18.75322493138122</v>
+        <v>19.02230140622725</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0.6938480609250613</v>
+        <v>0.5163316295136018</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L121" s="3" t="n">
         <v>0</v>
@@ -6885,7 +6885,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>-1.450101843068346</v>
+        <v>-0.2294428512641397</v>
       </c>
       <c r="O121" s="3" t="inlineStr">
         <is>
@@ -6895,21 +6895,21 @@
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>6958</v>
+        <v>7803</v>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
         <v/>
       </c>
       <c r="D122" s="3" t="n">
-        <v>103.4567097699689</v>
+        <v>125.7876630074972</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>16.85</v>
+        <v>22.7</v>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
@@ -6920,13 +6920,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>47.37940493976954</v>
+        <v>42.49598584445019</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>12.62337177094514</v>
+        <v>14.08288007446366</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>0.338787524777926</v>
+        <v>0.6736748085727162</v>
       </c>
       <c r="K122" s="3" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>0.0178464964728853</v>
+        <v>0.188236955834315</v>
       </c>
       <c r="O122" s="3" t="inlineStr">
         <is>
@@ -6948,21 +6948,21 @@
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>6908</v>
+        <v>6988</v>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
         <v/>
       </c>
       <c r="D123" s="3" t="n">
-        <v>98.64647374142034</v>
+        <v>118.3285876328881</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>36.6</v>
+        <v>13.6</v>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
@@ -6973,13 +6973,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>35.67848236633743</v>
+        <v>38.51959458816293</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>16.16135705159433</v>
+        <v>12.85521732756108</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>0.9148933175702304</v>
+        <v>0.8896812983225151</v>
       </c>
       <c r="K123" s="3" t="n">
         <v>0</v>
@@ -6991,7 +6991,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>-0.087356743294612</v>
+        <v>0.0530954262412654</v>
       </c>
       <c r="O123" s="3" t="inlineStr">
         <is>
@@ -7001,21 +7001,21 @@
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>7791</v>
+        <v>6895</v>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
         <v/>
       </c>
       <c r="D124" s="3" t="n">
-        <v>90.65151890781888</v>
+        <v>108.2004780325014</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>62.3</v>
+        <v>138</v>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
@@ -7026,16 +7026,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>44.12925873476573</v>
+        <v>34.33605711600157</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>12.97679447938762</v>
+        <v>18.75322493138122</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0.3751559636648389</v>
+        <v>0.6938480609250613</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L124" s="3" t="n">
         <v>0</v>
@@ -7044,7 +7044,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0.1468609124093213</v>
+        <v>-1.450101843068346</v>
       </c>
       <c r="O124" s="3" t="inlineStr">
         <is>
@@ -7054,21 +7054,21 @@
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>6885</v>
+        <v>6958</v>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
         <v/>
       </c>
       <c r="D125" s="3" t="n">
-        <v>75.27364768331685</v>
+        <v>103.4567097699689</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>21.85</v>
+        <v>16.85</v>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
@@ -7079,13 +7079,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>47.2964484181453</v>
+        <v>47.37940493976954</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>17.69471854958464</v>
+        <v>12.62337177094514</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0.4064297818704699</v>
+        <v>0.338787524777926</v>
       </c>
       <c r="K125" s="3" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0.0682610825202134</v>
+        <v>0.0178464964728853</v>
       </c>
       <c r="O125" s="3" t="inlineStr">
         <is>
@@ -7107,52 +7107,211 @@
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
+        <v>6908</v>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>宏碁遊戲-創</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>98.64647374142034</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>35.67848236633743</v>
+      </c>
+      <c r="I126" s="3" t="n">
+        <v>16.16135705159433</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>0.9148933175702304</v>
+      </c>
+      <c r="K126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="3" t="n">
+        <v>-0.087356743294612</v>
+      </c>
+      <c r="O126" s="3" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="n">
+        <v>7791</v>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>皇家可口</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>90.65151890781888</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="3" t="n">
+        <v>44.12925873476573</v>
+      </c>
+      <c r="I127" s="3" t="n">
+        <v>12.97679447938762</v>
+      </c>
+      <c r="J127" s="3" t="n">
+        <v>0.3751559636648389</v>
+      </c>
+      <c r="K127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="3" t="n">
+        <v>0.1468609124093213</v>
+      </c>
+      <c r="O127" s="3" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="n">
+        <v>6885</v>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>全福生技</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>75.27364768331685</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>47.2964484181453</v>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v>17.69471854958464</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>0.4064297818704699</v>
+      </c>
+      <c r="K128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="3" t="n">
+        <v>0.0682610825202134</v>
+      </c>
+      <c r="O128" s="3" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="n">
         <v>6921</v>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B129" s="3" t="inlineStr">
         <is>
           <t>嘉雨思-創</t>
         </is>
       </c>
-      <c r="C126" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D126" s="3" t="n">
+      <c r="C129" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="3" t="n">
         <v>56.6310574268157</v>
       </c>
-      <c r="E126" s="3" t="n">
+      <c r="E129" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H126" s="3" t="n">
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="3" t="n">
         <v>38.93343411596706</v>
       </c>
-      <c r="I126" s="3" t="n">
+      <c r="I129" s="3" t="n">
         <v>17.35227948019281</v>
       </c>
-      <c r="J126" s="3" t="n">
+      <c r="J129" s="3" t="n">
         <v>0.1668720314980874</v>
       </c>
-      <c r="K126" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N126" s="3" t="n">
+      <c r="K129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="3" t="n">
         <v>0.2385507695230706</v>
       </c>
-      <c r="O126" s="3" t="inlineStr">
+      <c r="O129" s="3" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq8_2026-07-09.xlsx
+++ b/output/full_scan/batch_seq8_2026-07-09.xlsx
@@ -1754,21 +1754,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6928</v>
+        <v>7402</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>660.356434821952</v>
+        <v>657.9599836910082</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>53.3</v>
+        <v>131</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1779,13 +1779,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>57.63566193007057</v>
+        <v>63.74607051890244</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>32.03870086834914</v>
+        <v>31.87193742892348</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4347882539286762</v>
+        <v>1.895998369100822</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1797,31 +1797,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.3178441433848018</v>
+        <v>3.251686895042466</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7402</v>
+        <v>6965</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>657.9599836910082</v>
+        <v>657.1843931304295</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1832,16 +1832,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>63.74607051890244</v>
+        <v>52.20498622387128</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31.87193742892348</v>
+        <v>22.25081504807666</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.895998369100822</v>
+        <v>0.5680626029119896</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1850,31 +1850,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>3.251686895042466</v>
+        <v>0.151930499100081</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6965</v>
+        <v>6890</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>657.1843931304295</v>
+        <v>655.1476617649607</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1885,49 +1885,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>52.20498622387128</v>
+        <v>47.04697220223746</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>22.25081504807666</v>
+        <v>18.8247603452546</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5680626029119896</v>
+        <v>0.9427276747293294</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.151930499100081</v>
+        <v>-4.348860042339972</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6890</v>
+        <v>7717</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>655.1476617649607</v>
+        <v>652.2429131338725</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>206</v>
+        <v>422.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1938,49 +1938,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>47.04697220223746</v>
+        <v>32.03154027332101</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>18.8247603452546</v>
+        <v>22.98215457332702</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.9427276747293294</v>
+        <v>0.2816613219084758</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-4.348860042339972</v>
+        <v>0.6582596039140114</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7717</v>
+        <v>6928</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>652.2429131338725</v>
+        <v>640.356434821952</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>422.5</v>
+        <v>53.3</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1991,13 +1991,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>32.03154027332101</v>
+        <v>57.63566193007057</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>22.98215457332702</v>
+        <v>32.03870086834914</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.2816613219084758</v>
+        <v>0.4347882539286762</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2009,11 +2009,11 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.6582596039140114</v>
+        <v>0.3178441433848018</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2125,21 +2125,21 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7799</v>
+        <v>6869</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>611.7499454937273</v>
+        <v>626.663640477753</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>435.5</v>
+        <v>71.2</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2150,16 +2150,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>60.12411481233664</v>
+        <v>38.86067094420142</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>38.59920649593993</v>
+        <v>26.10419623332139</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.475752415887216</v>
+        <v>0.5619937666619337</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2168,31 +2168,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>4.606444194655385</v>
+        <v>0.038093341404632</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6869</v>
+        <v>7799</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>606.663640477753</v>
+        <v>611.7499454937273</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>71.2</v>
+        <v>435.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2203,16 +2203,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>38.86067094420142</v>
+        <v>60.12411481233664</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>26.10419623332139</v>
+        <v>38.59920649593993</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5619937666619337</v>
+        <v>1.475752415887216</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2221,11 +2221,11 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.038093341404632</v>
+        <v>4.606444194655385</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2655,21 +2655,21 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6944</v>
+        <v>6870</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>518.5894468604549</v>
+        <v>518.5352456195039</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>998</v>
+        <v>289</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2680,16 +2680,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>53.97414304544137</v>
+        <v>54.18808299369103</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13.54217250930741</v>
+        <v>20.69329594231462</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.9308369947680232</v>
+        <v>0.1832728974954264</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2698,31 +2698,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-6.063096853992935</v>
+        <v>-0.7414892129802908</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6870</v>
+        <v>6902</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>518.5352456195039</v>
+        <v>508.7113474025167</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>289</v>
+        <v>137.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2733,16 +2733,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>54.18808299369103</v>
+        <v>55.36736361158736</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>20.69329594231462</v>
+        <v>20.10381370154674</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.1832728974954264</v>
+        <v>0.2329276147208781</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2751,31 +2751,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.7414892129802908</v>
+        <v>-0.3703481322627091</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6916</v>
+        <v>7770</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>513.6132347063674</v>
+        <v>492.5192228975166</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>20.15</v>
+        <v>42.6</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2786,13 +2786,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.45269420994582</v>
+        <v>49.23205470173506</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>18.77870919338771</v>
+        <v>6.990383305089063</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.212716101588165</v>
+        <v>0.3272373250852448</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2804,31 +2804,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.1541319074217235</v>
+        <v>0.1931446192736043</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6951</v>
+        <v>7753</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>509.1065317235509</v>
+        <v>487.9967932480413</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>78.7</v>
+        <v>42.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2839,16 +2839,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>47.44109769981664</v>
+        <v>49.18736334439472</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.92213186425082</v>
+        <v>25.08255245343453</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.246109337475753</v>
+        <v>0.2660209729607627</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2857,31 +2857,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.1838906479945109</v>
+        <v>-0.009245602312927001</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6902</v>
+        <v>6903</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>508.7113474025167</v>
+        <v>485.3920352556953</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>137.5</v>
+        <v>394</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2892,13 +2892,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>55.36736361158736</v>
+        <v>51.64959307743278</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>20.10381370154674</v>
+        <v>9.970553252553394</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.2329276147208781</v>
+        <v>1.369092394743471</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>1</v>
@@ -2910,31 +2910,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.3703481322627091</v>
+        <v>-0.2292449030543601</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7770</v>
+        <v>7842</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>492.5192228975166</v>
+        <v>480.8956004829969</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>42.6</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2945,16 +2945,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.23205470173506</v>
+        <v>39.15241912954303</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>6.990383305089063</v>
+        <v>20.35499744177083</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.3272373250852448</v>
+        <v>0.187849824274318</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2963,31 +2963,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.1931446192736043</v>
+        <v>0.9166581057404332</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7753</v>
+        <v>7821</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>487.9967932480413</v>
+        <v>479.9200867577227</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>42.5</v>
+        <v>41</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2998,16 +2998,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>49.18736334439472</v>
+        <v>34.1066205944374</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25.08255245343453</v>
+        <v>26.67316488192231</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.2660209729607627</v>
+        <v>0.3955972118325168</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3016,31 +3016,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.009245602312927001</v>
+        <v>-0.0368639804291439</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6933</v>
+        <v>6944</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>487.1411986314473</v>
+        <v>478.589446860455</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>157.5</v>
+        <v>998</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3051,16 +3051,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>53.73800873279094</v>
+        <v>53.97414304544137</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>18.85947881446384</v>
+        <v>13.54217250930741</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.9511992847274796</v>
+        <v>0.9308369947680232</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3069,31 +3069,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>1.07590935319981</v>
+        <v>-6.063096853992935</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6903</v>
+        <v>8043</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>485.3920352556953</v>
+        <v>475.7514469076053</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>394</v>
+        <v>173</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.64959307743278</v>
+        <v>46.70045581300656</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>9.970553252553394</v>
+        <v>26.68826088461669</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.369092394743471</v>
+        <v>0.402376190359628</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3122,31 +3122,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.2292449030543601</v>
+        <v>-6.202201158697672</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, williams_r_recovery, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7842</v>
+        <v>6916</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>480.8956004829969</v>
+        <v>473.6132347063673</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>97.40000000000001</v>
+        <v>20.15</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3157,16 +3157,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>39.15241912954303</v>
+        <v>49.45269420994582</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>20.35499744177083</v>
+        <v>18.77870919338771</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.187849824274318</v>
+        <v>0.212716101588165</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3175,31 +3175,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.9166581057404332</v>
+        <v>-0.1541319074217235</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7821</v>
+        <v>6951</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>479.9200867577227</v>
+        <v>469.1065317235509</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>41</v>
+        <v>78.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3210,16 +3210,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>34.1066205944374</v>
+        <v>47.44109769981664</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>26.67316488192231</v>
+        <v>21.92213186425082</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.3955972118325168</v>
+        <v>1.246109337475753</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3228,31 +3228,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0368639804291439</v>
+        <v>0.1838906479945109</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8043</v>
+        <v>7744</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>475.7514469076053</v>
+        <v>452.2739161503841</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>173</v>
+        <v>463</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3263,13 +3263,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>46.70045581300656</v>
+        <v>46.63510099871355</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>26.68826088461669</v>
+        <v>12.94767390585702</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.402376190359628</v>
+        <v>0.2186238196630761</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3281,31 +3281,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-6.202201158697672</v>
+        <v>2.634616974798769</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6924</v>
+        <v>7711</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>465.2868228989308</v>
+        <v>448.168402592468</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>130</v>
+        <v>307.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>51.38843437281255</v>
+        <v>33.58404498228191</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>16.82560710356251</v>
+        <v>23.32559148373669</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.082274986195472</v>
+        <v>0.3173966296746351</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3334,31 +3334,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.9410840027423416</v>
+        <v>-2.214144684909884</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7744</v>
+        <v>6933</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>452.2739161503841</v>
+        <v>447.1411986314473</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>463</v>
+        <v>157.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3369,13 +3369,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46.63510099871355</v>
+        <v>53.73800873279094</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12.94767390585702</v>
+        <v>18.85947881446384</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.2186238196630761</v>
+        <v>0.9511992847274796</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3387,31 +3387,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>2.634616974798769</v>
+        <v>1.07590935319981</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7711</v>
+        <v>6924</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>448.168402592468</v>
+        <v>445.2868228989308</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>307.5</v>
+        <v>130</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3422,16 +3422,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>33.58404498228191</v>
+        <v>51.38843437281255</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>23.32559148373669</v>
+        <v>16.82560710356251</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3173966296746351</v>
+        <v>1.082274986195472</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3440,11 +3440,11 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-2.214144684909884</v>
+        <v>0.9410840027423416</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -4351,21 +4351,21 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6923</v>
+        <v>6873</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>371.4682919561231</v>
+        <v>375.1231478298613</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4376,13 +4376,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>44.57626905084211</v>
+        <v>52.88983667921317</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>12.67822019372631</v>
+        <v>15.53961611986994</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.8082727665262706</v>
+        <v>0.569297001249601</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4394,31 +4394,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.2577025328151188</v>
+        <v>1.068271818973007</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7734</v>
+        <v>6862</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>370.4252442852194</v>
+        <v>375.0694609867115</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>2835</v>
+        <v>181.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4429,16 +4429,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>41.8126328774763</v>
+        <v>44.44859699964978</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15.66271258074686</v>
+        <v>18.98089112724713</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.2576035571302245</v>
+        <v>0.3280607157287171</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4447,31 +4447,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-41.22411777427128</v>
+        <v>-2.812789303812949</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6863</v>
+        <v>7734</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>370.0321392910109</v>
+        <v>370.4252442852194</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>92.8</v>
+        <v>2835</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4482,16 +4482,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>41.40054904091114</v>
+        <v>41.8126328774763</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.6022182794955</v>
+        <v>15.66271258074686</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.1941587514346871</v>
+        <v>0.2576035571302245</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4500,11 +4500,11 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.3684407432840513</v>
+        <v>-41.22411777427128</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
@@ -4563,21 +4563,21 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6937</v>
+        <v>6971</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>365.7484381391925</v>
+        <v>363.7964353379251</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>258.5</v>
+        <v>27.3</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4588,16 +4588,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>41.58821044298968</v>
+        <v>45.75591484800266</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>11.66045158694848</v>
+        <v>18.54081073089325</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5558910775457436</v>
+        <v>0.1202245018776939</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4606,31 +4606,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.2642627748224893</v>
+        <v>-0.0453578304074157</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6971</v>
+        <v>6877</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>363.7964353379251</v>
+        <v>363.3623638600944</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>27.3</v>
+        <v>132.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4641,16 +4641,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45.75591484800266</v>
+        <v>47.05222303674569</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.54081073089325</v>
+        <v>14.81593521141948</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.1202245018776939</v>
+        <v>0.305062344974368</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4659,31 +4659,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0453578304074157</v>
+        <v>1.002289235069908</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6877</v>
+        <v>6936</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>363.3623638600944</v>
+        <v>360.5870156353577</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>132.5</v>
+        <v>32.65</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4694,13 +4694,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>47.05222303674569</v>
+        <v>42.20126496160968</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.81593521141948</v>
+        <v>13.17221900359745</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.305062344974368</v>
+        <v>4.046462224784912</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>2</v>
@@ -4712,31 +4712,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.002289235069908</v>
+        <v>0.0428852394046692</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6936</v>
+        <v>7747</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>360.5870156353577</v>
+        <v>359.7446520819408</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>32.65</v>
+        <v>129</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4747,16 +4747,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.20126496160968</v>
+        <v>51.76962879405791</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.17221900359745</v>
+        <v>4.196623507404667</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>4.046462224784912</v>
+        <v>0.2290081313536389</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4765,31 +4765,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0428852394046692</v>
+        <v>-0.1267747152922331</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7747</v>
+        <v>6983</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>359.7446520819408</v>
+        <v>358.0912332595235</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>129</v>
+        <v>349.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4800,13 +4800,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>51.76962879405791</v>
+        <v>44.35696361357847</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>4.196623507404667</v>
+        <v>10.04619420799603</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.2290081313536389</v>
+        <v>0.3081349841485361</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4818,31 +4818,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.1267747152922331</v>
+        <v>0.69084471980422</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6983</v>
+        <v>7740</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>358.0912332595235</v>
+        <v>357.9738466243005</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>349.5</v>
+        <v>147.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4853,16 +4853,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>44.35696361357847</v>
+        <v>40.20243596528031</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>10.04619420799603</v>
+        <v>19.02230141015969</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3081349841485361</v>
+        <v>0.5163316295136018</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4871,31 +4871,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.69084471980422</v>
+        <v>-0.2294428513595576</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7740</v>
+        <v>7765</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>357.9738466243005</v>
+        <v>356.3177662010121</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>147.5</v>
+        <v>221.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4906,16 +4906,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>40.20243596528031</v>
+        <v>38.25188507101979</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>19.02230141015969</v>
+        <v>20.95841076203018</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5163316295136018</v>
+        <v>0.4169676386477593</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4924,31 +4924,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.2294428513595576</v>
+        <v>-0.2425739004286047</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7765</v>
+        <v>6914</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>356.3177662010121</v>
+        <v>351.6461908947728</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>221.5</v>
+        <v>142.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>38.25188507101979</v>
+        <v>46.91513569723856</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>20.95841076203018</v>
+        <v>9.301055141744916</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4169676386477593</v>
+        <v>0.6707749528069579</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4977,31 +4977,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.2425739004286047</v>
+        <v>0.06783348748948009</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6873</v>
+        <v>7704</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>355.1231478298612</v>
+        <v>345.9775013456459</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>86.59999999999999</v>
+        <v>60</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5012,13 +5012,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>52.88983667921317</v>
+        <v>43.08052754930262</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15.53961611986994</v>
+        <v>10.35003673546126</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.569297001249601</v>
+        <v>0.4674774304936214</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5030,31 +5030,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>1.068271818973007</v>
+        <v>-0.2137068832335129</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6914</v>
+        <v>7792</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>351.6461908947728</v>
+        <v>342.0459665854466</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>142.5</v>
+        <v>235.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5065,16 +5065,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>46.91513569723856</v>
+        <v>33.84481336908068</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>9.301055141744916</v>
+        <v>21.04219704037088</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.6707749528069579</v>
+        <v>0.4424815915393387</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5083,31 +5083,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.06783348748948009</v>
+        <v>-1.195066356704928</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>7704</v>
+        <v>6855</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>345.9775013456459</v>
+        <v>337.4605930448236</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>43.08052754930262</v>
+        <v>52.29651938628686</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>10.35003673546126</v>
+        <v>8.04114534922557</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4674774304936214</v>
+        <v>0.6924604135392959</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5136,31 +5136,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.2137068832335129</v>
+        <v>0.4306449892046662</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6862</v>
+        <v>7728</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>345.0694609867115</v>
+        <v>332.3704498635813</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>181.5</v>
+        <v>654</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5171,16 +5171,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>44.44859699964978</v>
+        <v>42.17218319386206</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>18.98089112724713</v>
+        <v>11.88058741850058</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.3280607157287171</v>
+        <v>0.2558557370213209</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5189,31 +5189,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-2.812789303812949</v>
+        <v>-2.451909478079361</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>7792</v>
+        <v>6923</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>342.0459665854466</v>
+        <v>331.4682919561231</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>235.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5224,13 +5224,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>33.84481336908068</v>
+        <v>44.57626905084211</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>21.04219704037088</v>
+        <v>12.67822019372631</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4424815915393387</v>
+        <v>0.8082727665262706</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5242,31 +5242,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-1.195066356704928</v>
+        <v>0.2577025328151188</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6855</v>
+        <v>6863</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>337.4605930448236</v>
+        <v>330.0321392910109</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>122</v>
+        <v>92.8</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5277,16 +5277,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>52.29651938628686</v>
+        <v>41.40054904091114</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>8.04114534922557</v>
+        <v>20.6022182794955</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6924604135392959</v>
+        <v>0.1941587514346871</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5295,31 +5295,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.4306449892046662</v>
+        <v>0.3684407432840513</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7728</v>
+        <v>6937</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>332.3704498635813</v>
+        <v>325.7484381391925</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>654</v>
+        <v>258.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5330,16 +5330,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>42.17218319386206</v>
+        <v>41.58821044298968</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11.88058741850058</v>
+        <v>11.66045158694848</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.2558557370213209</v>
+        <v>0.5558910775457436</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5348,31 +5348,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-2.451909478079361</v>
+        <v>-0.2642627748224893</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6887</v>
+        <v>7751</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>328.9710633676277</v>
+        <v>324.4173100399416</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>33.8</v>
+        <v>1295</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5383,16 +5383,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.48886169883458</v>
+        <v>39.44757102375637</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>5.139339190518846</v>
+        <v>9.860766948779018</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.6399454679385927</v>
+        <v>1.476844180607912</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5401,31 +5401,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1638936681527898</v>
+        <v>8.145777824020414</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7751</v>
+        <v>8047</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>324.4173100399416</v>
+        <v>322.5700999515211</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>1295</v>
+        <v>44</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5436,16 +5436,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>39.44757102375637</v>
+        <v>39.94849770984634</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>9.860766948779018</v>
+        <v>7.110162534599978</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.476844180607912</v>
+        <v>0.8073288779987986</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5454,31 +5454,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>8.145777824020414</v>
+        <v>-0.5620929104613687</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8047</v>
+        <v>8045</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>322.5700999515211</v>
+        <v>320.8412753222526</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>44</v>
+        <v>58.4</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5489,13 +5489,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>39.94849770984634</v>
+        <v>38.28273749110956</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>7.110162534599978</v>
+        <v>11.24634823146596</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8073288779987986</v>
+        <v>0.7578615350408903</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>1</v>
@@ -5507,31 +5507,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.5620929104613687</v>
+        <v>0.1666947706218837</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8045</v>
+        <v>6887</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>320.8412753222526</v>
+        <v>308.9710633676277</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>58.4</v>
+        <v>33.8</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5542,13 +5542,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>38.28273749110956</v>
+        <v>45.48886169883458</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.24634823146596</v>
+        <v>5.139339190518846</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.7578615350408903</v>
+        <v>0.6399454679385927</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>1</v>
@@ -5560,31 +5560,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1666947706218837</v>
+        <v>-0.1638936681527898</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6854</v>
+        <v>7736</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>307.9321804976679</v>
+        <v>304.467327106767</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>113.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5595,16 +5595,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>29.76518114133657</v>
+        <v>41.22229868003949</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>23.47971786607372</v>
+        <v>13.28760285875499</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.527707214277649</v>
+        <v>0.8334829319487406</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5613,31 +5613,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1925840124130724</v>
+        <v>0.0114340746977891</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7736</v>
+        <v>8032</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>304.467327106767</v>
+        <v>301.7152547634907</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>70.40000000000001</v>
+        <v>41.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5648,16 +5648,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>41.22229868003949</v>
+        <v>41.29813014855965</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>13.28760285875499</v>
+        <v>19.24859766789432</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8334829319487406</v>
+        <v>0.1251730459362888</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5666,31 +5666,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0114340746977891</v>
+        <v>-0.4744961205503365</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8032</v>
+        <v>6906</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>301.7152547634907</v>
+        <v>298.577190325238</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>41.8</v>
+        <v>82</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5701,16 +5701,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>41.29813014855965</v>
+        <v>39.51278555185927</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>19.24859766789432</v>
+        <v>17.85269472786651</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.1251730459362888</v>
+        <v>0.3971803849544118</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5719,7 +5719,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.4744961205503365</v>
+        <v>-1.468828733260629</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5729,21 +5729,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6906</v>
+        <v>6918</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>298.577190325238</v>
+        <v>297.0850751975527</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>82</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5754,13 +5754,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>39.51278555185927</v>
+        <v>52.23885075978043</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.85269472786651</v>
+        <v>13.4830962017074</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3971803849544118</v>
+        <v>0.4409605856337868</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>1</v>
@@ -5772,31 +5772,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.468828733260629</v>
+        <v>0.1896822961093553</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6918</v>
+        <v>6931</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>297.0850751975527</v>
+        <v>296.6313441542502</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>74.09999999999999</v>
+        <v>39.75</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5807,13 +5807,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>52.23885075978043</v>
+        <v>40.62086957529913</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>13.4830962017074</v>
+        <v>17.3503840018668</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.4409605856337868</v>
+        <v>0.5679778257363548</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>1</v>
@@ -5825,7 +5825,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.1896822961093553</v>
+        <v>0.068982221357753</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5835,21 +5835,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6931</v>
+        <v>7721</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>296.6313441542502</v>
+        <v>294.8380842922334</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>39.75</v>
+        <v>71</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5860,16 +5860,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>40.62086957529913</v>
+        <v>44.80168470812589</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17.3503840018668</v>
+        <v>10.93154352012251</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.5679778257363548</v>
+        <v>0.1445584497526122</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5878,31 +5878,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.068982221357753</v>
+        <v>-0.2848709066211199</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7721</v>
+        <v>6967</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>294.8380842922334</v>
+        <v>294.6658513074201</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>71</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5913,13 +5913,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>44.80168470812589</v>
+        <v>43.2632513968686</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>10.93154352012251</v>
+        <v>12.28915740397964</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.1445584497526122</v>
+        <v>0.6501533329938837</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5931,31 +5931,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.2848709066211199</v>
+        <v>-0.1277832835988867</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6967</v>
+        <v>6854</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>294.6658513074201</v>
+        <v>287.9321804976679</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>113.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5966,13 +5966,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>43.2632513968686</v>
+        <v>29.76518114133657</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.28915740397964</v>
+        <v>23.47971786607372</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.6501533329938837</v>
+        <v>1.527707214277649</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5984,11 +5984,11 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.1277832835988867</v>
+        <v>-0.1925840124130724</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
@@ -6418,21 +6418,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6909</v>
+        <v>6908</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>257.2207977387619</v>
+        <v>243.6464737414201</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>51.3</v>
+        <v>36.6</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6443,13 +6443,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>44.84173236254644</v>
+        <v>35.67848240626194</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.43522249029083</v>
+        <v>16.1613569677956</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.2418643455155242</v>
+        <v>0.9148933175702304</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6461,11 +6461,11 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.4028328879516456</v>
+        <v>-0.08735674367619881</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
@@ -6630,21 +6630,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6899</v>
+        <v>6921</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>218.6683684623978</v>
+        <v>226.6310574268157</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>54.7</v>
+        <v>68</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6655,13 +6655,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>34.04625825395961</v>
+        <v>38.93343411596706</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>14.93820479383245</v>
+        <v>17.35227948019281</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.9242118449439766</v>
+        <v>0.1668720314980874</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6673,31 +6673,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.3323764673576509</v>
+        <v>0.2385507695230706</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7749</v>
+        <v>6899</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>216.15866189966</v>
+        <v>218.6683684623978</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>404</v>
+        <v>54.7</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6708,13 +6708,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>34.08472250739553</v>
+        <v>34.04625825395961</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>15.49490569347116</v>
+        <v>14.93820479383245</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.2834734020563929</v>
+        <v>0.9242118449439766</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6726,31 +6726,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-4.924311626850146</v>
+        <v>-0.3323764673576509</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6885</v>
+        <v>6909</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>215.2736476833169</v>
+        <v>217.220797738762</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>21.85</v>
+        <v>51.3</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6761,16 +6761,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>47.2964484181453</v>
+        <v>44.84173236254644</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>17.69471854733938</v>
+        <v>16.43522249029083</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.4064297818704699</v>
+        <v>0.2418643455155242</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6779,31 +6779,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.06826108265377059</v>
+        <v>-0.4028328879516456</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>8044</v>
+        <v>7749</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>214.1764594044797</v>
+        <v>216.15866189966</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>26.8</v>
+        <v>404</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6814,13 +6814,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>41.52098254858291</v>
+        <v>34.08472250739553</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>14.18891225190132</v>
+        <v>15.49490569347116</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.2486213192443414</v>
+        <v>0.2834734020563929</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6832,31 +6832,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.3977575223101354</v>
+        <v>-4.924311626850146</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6908</v>
+        <v>6885</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>213.6464737414201</v>
+        <v>215.2736476833169</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>36.6</v>
+        <v>21.85</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6867,16 +6867,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>35.67848240626194</v>
+        <v>47.2964484181453</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>16.1613569677956</v>
+        <v>17.69471854733938</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.9148933175702304</v>
+        <v>0.4064297818704699</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6885,7 +6885,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.08735674367619881</v>
+        <v>0.06826108265377059</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6895,21 +6895,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>7730</v>
+        <v>8044</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>209.1135777707526</v>
+        <v>214.1764594044797</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>183</v>
+        <v>26.8</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6920,13 +6920,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>47.84907312567253</v>
+        <v>41.52098254858291</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>10.27348699793313</v>
+        <v>14.18891225190132</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.9215102340619056</v>
+        <v>0.2486213192443414</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6938,31 +6938,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.4485259988977426</v>
+        <v>-0.3977575223101354</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6953</v>
+        <v>7730</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>202.7766110895432</v>
+        <v>209.1135777707526</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>228</v>
+        <v>183</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6973,13 +6973,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>43.79332010999956</v>
+        <v>47.84907312567253</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>12.77746564868914</v>
+        <v>10.27348699793313</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.3861295447556247</v>
+        <v>0.9215102340619056</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6991,7 +6991,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.2059930994131873</v>
+        <v>0.4485259988977426</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7001,21 +7001,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6859</v>
+        <v>6953</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>202.4637793579379</v>
+        <v>202.7766110895432</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>120.5</v>
+        <v>228</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7026,13 +7026,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>42.96529548176591</v>
+        <v>43.79332010999956</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>15.9452175682549</v>
+        <v>12.77746564868914</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.1066902570738212</v>
+        <v>0.3861295447556247</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7044,31 +7044,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-1.061681770343376</v>
+        <v>0.2059930994131873</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6921</v>
+        <v>6859</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>196.6310574268157</v>
+        <v>202.4637793579379</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>68</v>
+        <v>120.5</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7079,13 +7079,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>38.93343411596706</v>
+        <v>42.96529548176591</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>17.35227948019281</v>
+        <v>15.9452175682549</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.1668720314980874</v>
+        <v>0.1066902570738212</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7097,11 +7097,11 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.2385507695230706</v>
+        <v>-1.061681770343376</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq8_2026-07-09.xlsx
+++ b/output/full_scan/batch_seq8_2026-07-09.xlsx
@@ -1754,21 +1754,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>7402</v>
+        <v>6928</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>657.9599836910082</v>
+        <v>660.356434821952</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>131</v>
+        <v>53.3</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1779,13 +1779,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.74607051890244</v>
+        <v>57.63566193007057</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>31.87193742892348</v>
+        <v>32.03870086834914</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.895998369100822</v>
+        <v>0.4347882539286762</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1797,31 +1797,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>3.251686895042466</v>
+        <v>0.3178441433848018</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6965</v>
+        <v>7402</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>657.1843931304295</v>
+        <v>657.9599836910082</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1832,16 +1832,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>52.20498622387128</v>
+        <v>63.74607051890244</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>22.25081504807666</v>
+        <v>31.87193742892348</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5680626029119896</v>
+        <v>1.895998369100822</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1850,31 +1850,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.151930499100081</v>
+        <v>3.251686895042466</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6890</v>
+        <v>6965</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>655.1476617649607</v>
+        <v>657.1843931304295</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>206</v>
+        <v>80</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1885,49 +1885,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>47.04697220223746</v>
+        <v>52.20498622387128</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>18.8247603452546</v>
+        <v>22.25081504807666</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.9427276747293294</v>
+        <v>0.5680626029119896</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-4.348860042339972</v>
+        <v>0.151930499100081</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7717</v>
+        <v>6890</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>652.2429131338725</v>
+        <v>655.1476617649607</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>422.5</v>
+        <v>206</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1938,49 +1938,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>32.03154027332101</v>
+        <v>47.04697220223746</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>22.98215457332702</v>
+        <v>18.8247603452546</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.2816613219084758</v>
+        <v>0.9427276747293294</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.6582596039140114</v>
+        <v>-4.348860042339972</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6928</v>
+        <v>7717</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>640.356434821952</v>
+        <v>652.2429131338725</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>53.3</v>
+        <v>422.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1991,13 +1991,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>57.63566193007057</v>
+        <v>32.03154027332101</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>32.03870086834914</v>
+        <v>22.98215457332702</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4347882539286762</v>
+        <v>0.2816613219084758</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2009,11 +2009,11 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3178441433848018</v>
+        <v>0.6582596039140114</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
@@ -2125,21 +2125,21 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6869</v>
+        <v>7799</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>626.663640477753</v>
+        <v>611.7499454937273</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>71.2</v>
+        <v>435.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2150,16 +2150,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>38.86067094420142</v>
+        <v>60.12411481233664</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26.10419623332139</v>
+        <v>38.59920649593993</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5619937666619337</v>
+        <v>1.475752415887216</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2168,31 +2168,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.038093341404632</v>
+        <v>4.606444194655385</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7799</v>
+        <v>6869</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>611.7499454937273</v>
+        <v>606.663640477753</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>435.5</v>
+        <v>71.2</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2203,16 +2203,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>60.12411481233664</v>
+        <v>38.86067094420142</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>38.59920649593993</v>
+        <v>26.10419623332139</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.475752415887216</v>
+        <v>0.5619937666619337</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2221,11 +2221,11 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>4.606444194655385</v>
+        <v>0.038093341404632</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
@@ -2655,21 +2655,21 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6870</v>
+        <v>6944</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>518.5352456195039</v>
+        <v>518.5894468604549</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>289</v>
+        <v>998</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2680,16 +2680,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>54.18808299369103</v>
+        <v>53.97414304544137</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>20.69329594231462</v>
+        <v>13.54217250930741</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.1832728974954264</v>
+        <v>0.9308369947680232</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2698,31 +2698,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.7414892129802908</v>
+        <v>-6.063096853992935</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6902</v>
+        <v>6870</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>508.7113474025167</v>
+        <v>518.5352456195039</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>137.5</v>
+        <v>289</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2733,16 +2733,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>55.36736361158736</v>
+        <v>54.18808299369103</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>20.10381370154674</v>
+        <v>20.69329594231462</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.2329276147208781</v>
+        <v>0.1832728974954264</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2751,31 +2751,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.3703481322627091</v>
+        <v>-0.7414892129802908</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7770</v>
+        <v>6916</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>492.5192228975166</v>
+        <v>513.6132347063674</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>42.6</v>
+        <v>20.15</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2786,13 +2786,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.23205470173506</v>
+        <v>49.45269420994582</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>6.990383305089063</v>
+        <v>18.77870919338771</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3272373250852448</v>
+        <v>0.212716101588165</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2804,31 +2804,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1931446192736043</v>
+        <v>-0.1541319074217235</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7753</v>
+        <v>6951</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>487.9967932480413</v>
+        <v>509.1065317235509</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>42.5</v>
+        <v>78.7</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2839,16 +2839,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>49.18736334439472</v>
+        <v>47.44109769981664</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>25.08255245343453</v>
+        <v>21.92213186425082</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2660209729607627</v>
+        <v>1.246109337475753</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2857,31 +2857,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.009245602312927001</v>
+        <v>0.1838906479945109</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6903</v>
+        <v>6902</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>485.3920352556953</v>
+        <v>508.7113474025167</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>394</v>
+        <v>137.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2892,13 +2892,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.64959307743278</v>
+        <v>55.36736361158736</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9.970553252553394</v>
+        <v>20.10381370154674</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.369092394743471</v>
+        <v>0.2329276147208781</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>1</v>
@@ -2910,31 +2910,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.2292449030543601</v>
+        <v>-0.3703481322627091</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, williams_r_recovery, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7842</v>
+        <v>7770</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>480.8956004829969</v>
+        <v>492.5192228975166</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>97.40000000000001</v>
+        <v>42.6</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2945,16 +2945,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>39.15241912954303</v>
+        <v>49.23205470173506</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>20.35499744177083</v>
+        <v>6.990383305089063</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.187849824274318</v>
+        <v>0.3272373250852448</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2963,31 +2963,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.9166581057404332</v>
+        <v>0.1931446192736043</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7821</v>
+        <v>7753</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>479.9200867577227</v>
+        <v>487.9967932480413</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>41</v>
+        <v>42.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2998,16 +2998,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>34.1066205944374</v>
+        <v>49.18736334439472</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>26.67316488192231</v>
+        <v>25.08255245343453</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3955972118325168</v>
+        <v>0.2660209729607627</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3016,31 +3016,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0368639804291439</v>
+        <v>-0.009245602312927001</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6944</v>
+        <v>6933</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>478.589446860455</v>
+        <v>487.1411986314473</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>998</v>
+        <v>157.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3051,16 +3051,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>53.97414304544137</v>
+        <v>53.73800873279094</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.54217250930741</v>
+        <v>18.85947881446384</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.9308369947680232</v>
+        <v>0.9511992847274796</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3069,31 +3069,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-6.063096853992935</v>
+        <v>1.07590935319981</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8043</v>
+        <v>6903</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>475.7514469076053</v>
+        <v>485.3920352556953</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>173</v>
+        <v>394</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>46.70045581300656</v>
+        <v>51.64959307743278</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>26.68826088461669</v>
+        <v>9.970553252553394</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.402376190359628</v>
+        <v>1.369092394743471</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3122,31 +3122,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-6.202201158697672</v>
+        <v>-0.2292449030543601</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6916</v>
+        <v>7842</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>473.6132347063673</v>
+        <v>480.8956004829969</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>20.15</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3157,16 +3157,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.45269420994582</v>
+        <v>39.15241912954303</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>18.77870919338771</v>
+        <v>20.35499744177083</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.212716101588165</v>
+        <v>0.187849824274318</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3175,31 +3175,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.1541319074217235</v>
+        <v>0.9166581057404332</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6951</v>
+        <v>7821</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>469.1065317235509</v>
+        <v>479.9200867577227</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>78.7</v>
+        <v>41</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3210,16 +3210,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>47.44109769981664</v>
+        <v>34.1066205944374</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>21.92213186425082</v>
+        <v>26.67316488192231</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.246109337475753</v>
+        <v>0.3955972118325168</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3228,31 +3228,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.1838906479945109</v>
+        <v>-0.0368639804291439</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7744</v>
+        <v>8043</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>452.2739161503841</v>
+        <v>475.7514469076053</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>463</v>
+        <v>173</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3263,13 +3263,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>46.63510099871355</v>
+        <v>46.70045581300656</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>12.94767390585702</v>
+        <v>26.68826088461669</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2186238196630761</v>
+        <v>0.402376190359628</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3281,31 +3281,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>2.634616974798769</v>
+        <v>-6.202201158697672</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>7711</v>
+        <v>6924</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>448.168402592468</v>
+        <v>465.2868228989308</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>307.5</v>
+        <v>130</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>33.58404498228191</v>
+        <v>51.38843437281255</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>23.32559148373669</v>
+        <v>16.82560710356251</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.3173966296746351</v>
+        <v>1.082274986195472</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3334,31 +3334,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-2.214144684909884</v>
+        <v>0.9410840027423416</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6933</v>
+        <v>7744</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>447.1411986314473</v>
+        <v>452.2739161503841</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>157.5</v>
+        <v>463</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3369,13 +3369,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>53.73800873279094</v>
+        <v>46.63510099871355</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18.85947881446384</v>
+        <v>12.94767390585702</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9511992847274796</v>
+        <v>0.2186238196630761</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3387,31 +3387,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1.07590935319981</v>
+        <v>2.634616974798769</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6924</v>
+        <v>7711</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>445.2868228989308</v>
+        <v>448.168402592468</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>130</v>
+        <v>307.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3422,16 +3422,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>51.38843437281255</v>
+        <v>33.58404498228191</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>16.82560710356251</v>
+        <v>23.32559148373669</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.082274986195472</v>
+        <v>0.3173966296746351</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3440,11 +3440,11 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.9410840027423416</v>
+        <v>-2.214144684909884</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -4351,21 +4351,21 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6873</v>
+        <v>6923</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>375.1231478298613</v>
+        <v>371.4682919561231</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>86.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4376,13 +4376,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>52.88983667921317</v>
+        <v>44.57626905084211</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15.53961611986994</v>
+        <v>12.67822019372631</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.569297001249601</v>
+        <v>0.8082727665262706</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4394,31 +4394,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1.068271818973007</v>
+        <v>0.2577025328151188</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6862</v>
+        <v>7734</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>375.0694609867115</v>
+        <v>370.4252442852194</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>181.5</v>
+        <v>2835</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4429,16 +4429,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>44.44859699964978</v>
+        <v>41.8126328774763</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>18.98089112724713</v>
+        <v>15.66271258074686</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.3280607157287171</v>
+        <v>0.2576035571302245</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4447,31 +4447,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-2.812789303812949</v>
+        <v>-41.22411777427128</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7734</v>
+        <v>6863</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>370.4252442852194</v>
+        <v>370.0321392910109</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>2835</v>
+        <v>92.8</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4482,16 +4482,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>41.8126328774763</v>
+        <v>41.40054904091114</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15.66271258074686</v>
+        <v>20.6022182794955</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.2576035571302245</v>
+        <v>0.1941587514346871</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4500,11 +4500,11 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-41.22411777427128</v>
+        <v>0.3684407432840513</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
@@ -4563,21 +4563,21 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6971</v>
+        <v>6937</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>363.7964353379251</v>
+        <v>365.7484381391925</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>27.3</v>
+        <v>258.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4588,16 +4588,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45.75591484800266</v>
+        <v>41.58821044298968</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.54081073089325</v>
+        <v>11.66045158694848</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.1202245018776939</v>
+        <v>0.5558910775457436</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4606,31 +4606,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0453578304074157</v>
+        <v>-0.2642627748224893</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6877</v>
+        <v>6971</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>363.3623638600944</v>
+        <v>363.7964353379251</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>132.5</v>
+        <v>27.3</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4641,16 +4641,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>47.05222303674569</v>
+        <v>45.75591484800266</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14.81593521141948</v>
+        <v>18.54081073089325</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.305062344974368</v>
+        <v>0.1202245018776939</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4659,31 +4659,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>1.002289235069908</v>
+        <v>-0.0453578304074157</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6936</v>
+        <v>6877</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>360.5870156353577</v>
+        <v>363.3623638600944</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>32.65</v>
+        <v>132.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4694,13 +4694,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>42.20126496160968</v>
+        <v>47.05222303674569</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>13.17221900359745</v>
+        <v>14.81593521141948</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>4.046462224784912</v>
+        <v>0.305062344974368</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>2</v>
@@ -4712,31 +4712,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0428852394046692</v>
+        <v>1.002289235069908</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7747</v>
+        <v>6936</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>359.7446520819408</v>
+        <v>360.5870156353577</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>129</v>
+        <v>32.65</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4747,16 +4747,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>51.76962879405791</v>
+        <v>42.20126496160968</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>4.196623507404667</v>
+        <v>13.17221900359745</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2290081313536389</v>
+        <v>4.046462224784912</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4765,31 +4765,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1267747152922331</v>
+        <v>0.0428852394046692</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6983</v>
+        <v>7747</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>358.0912332595235</v>
+        <v>359.7446520819408</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>349.5</v>
+        <v>129</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4800,13 +4800,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>44.35696361357847</v>
+        <v>51.76962879405791</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>10.04619420799603</v>
+        <v>4.196623507404667</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.3081349841485361</v>
+        <v>0.2290081313536389</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4818,31 +4818,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.69084471980422</v>
+        <v>-0.1267747152922331</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>7740</v>
+        <v>6983</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>357.9738466243005</v>
+        <v>358.0912332595235</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>147.5</v>
+        <v>349.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4853,16 +4853,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>40.20243596528031</v>
+        <v>44.35696361357847</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19.02230141015969</v>
+        <v>10.04619420799603</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5163316295136018</v>
+        <v>0.3081349841485361</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4871,31 +4871,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.2294428513595576</v>
+        <v>0.69084471980422</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7765</v>
+        <v>7740</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>356.3177662010121</v>
+        <v>357.9738466243005</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>221.5</v>
+        <v>147.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4906,16 +4906,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>38.25188507101979</v>
+        <v>40.20243596528031</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>20.95841076203018</v>
+        <v>19.02230141015969</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4169676386477593</v>
+        <v>0.5163316295136018</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4924,31 +4924,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.2425739004286047</v>
+        <v>-0.2294428513595576</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6914</v>
+        <v>7765</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>351.6461908947728</v>
+        <v>356.3177662010121</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>142.5</v>
+        <v>221.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4959,16 +4959,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46.91513569723856</v>
+        <v>38.25188507101979</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>9.301055141744916</v>
+        <v>20.95841076203018</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.6707749528069579</v>
+        <v>0.4169676386477593</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4977,31 +4977,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.06783348748948009</v>
+        <v>-0.2425739004286047</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>7704</v>
+        <v>6873</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>345.9775013456459</v>
+        <v>355.1231478298612</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>60</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5012,13 +5012,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>43.08052754930262</v>
+        <v>52.88983667921317</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>10.35003673546126</v>
+        <v>15.53961611986994</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4674774304936214</v>
+        <v>0.569297001249601</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5030,31 +5030,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.2137068832335129</v>
+        <v>1.068271818973007</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>7792</v>
+        <v>6914</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>342.0459665854466</v>
+        <v>351.6461908947728</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>235.5</v>
+        <v>142.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5065,16 +5065,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>33.84481336908068</v>
+        <v>46.91513569723856</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>21.04219704037088</v>
+        <v>9.301055141744916</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4424815915393387</v>
+        <v>0.6707749528069579</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5083,31 +5083,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-1.195066356704928</v>
+        <v>0.06783348748948009</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6855</v>
+        <v>7704</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>337.4605930448236</v>
+        <v>345.9775013456459</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>52.29651938628686</v>
+        <v>43.08052754930262</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>8.04114534922557</v>
+        <v>10.35003673546126</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.6924604135392959</v>
+        <v>0.4674774304936214</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5136,31 +5136,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.4306449892046662</v>
+        <v>-0.2137068832335129</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7728</v>
+        <v>6862</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>332.3704498635813</v>
+        <v>345.0694609867115</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>654</v>
+        <v>181.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5171,16 +5171,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>42.17218319386206</v>
+        <v>44.44859699964978</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.88058741850058</v>
+        <v>18.98089112724713</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.2558557370213209</v>
+        <v>0.3280607157287171</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5189,31 +5189,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-2.451909478079361</v>
+        <v>-2.812789303812949</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6923</v>
+        <v>7792</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>331.4682919561231</v>
+        <v>342.0459665854466</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>235.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5224,13 +5224,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>44.57626905084211</v>
+        <v>33.84481336908068</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12.67822019372631</v>
+        <v>21.04219704037088</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.8082727665262706</v>
+        <v>0.4424815915393387</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5242,31 +5242,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.2577025328151188</v>
+        <v>-1.195066356704928</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6863</v>
+        <v>6855</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>330.0321392910109</v>
+        <v>337.4605930448236</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>92.8</v>
+        <v>122</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5277,16 +5277,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>41.40054904091114</v>
+        <v>52.29651938628686</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>20.6022182794955</v>
+        <v>8.04114534922557</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.1941587514346871</v>
+        <v>0.6924604135392959</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5295,31 +5295,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.3684407432840513</v>
+        <v>0.4306449892046662</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6937</v>
+        <v>7728</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>325.7484381391925</v>
+        <v>332.3704498635813</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>258.5</v>
+        <v>654</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5330,16 +5330,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>41.58821044298968</v>
+        <v>42.17218319386206</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11.66045158694848</v>
+        <v>11.88058741850058</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5558910775457436</v>
+        <v>0.2558557370213209</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5348,31 +5348,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.2642627748224893</v>
+        <v>-2.451909478079361</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>7751</v>
+        <v>6887</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>324.4173100399416</v>
+        <v>328.9710633676277</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>1295</v>
+        <v>33.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5383,16 +5383,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>39.44757102375637</v>
+        <v>45.48886169883458</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>9.860766948779018</v>
+        <v>5.139339190518846</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.476844180607912</v>
+        <v>0.6399454679385927</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5401,31 +5401,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>8.145777824020414</v>
+        <v>-0.1638936681527898</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8047</v>
+        <v>7751</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>322.5700999515211</v>
+        <v>324.4173100399416</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>44</v>
+        <v>1295</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5436,16 +5436,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>39.94849770984634</v>
+        <v>39.44757102375637</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>7.110162534599978</v>
+        <v>9.860766948779018</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.8073288779987986</v>
+        <v>1.476844180607912</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5454,31 +5454,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.5620929104613687</v>
+        <v>8.145777824020414</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8045</v>
+        <v>8047</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>320.8412753222526</v>
+        <v>322.5700999515211</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>58.4</v>
+        <v>44</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5489,13 +5489,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>38.28273749110956</v>
+        <v>39.94849770984634</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>11.24634823146596</v>
+        <v>7.110162534599978</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.7578615350408903</v>
+        <v>0.8073288779987986</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>1</v>
@@ -5507,31 +5507,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1666947706218837</v>
+        <v>-0.5620929104613687</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6887</v>
+        <v>8045</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>308.9710633676277</v>
+        <v>320.8412753222526</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>33.8</v>
+        <v>58.4</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5542,13 +5542,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45.48886169883458</v>
+        <v>38.28273749110956</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>5.139339190518846</v>
+        <v>11.24634823146596</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6399454679385927</v>
+        <v>0.7578615350408903</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>1</v>
@@ -5560,31 +5560,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1638936681527898</v>
+        <v>0.1666947706218837</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7736</v>
+        <v>6854</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>304.467327106767</v>
+        <v>307.9321804976679</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>70.40000000000001</v>
+        <v>113.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5595,16 +5595,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>41.22229868003949</v>
+        <v>29.76518114133657</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13.28760285875499</v>
+        <v>23.47971786607372</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.8334829319487406</v>
+        <v>1.527707214277649</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5613,31 +5613,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0114340746977891</v>
+        <v>-0.1925840124130724</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8032</v>
+        <v>7736</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>301.7152547634907</v>
+        <v>304.467327106767</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>41.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5648,16 +5648,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>41.29813014855965</v>
+        <v>41.22229868003949</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>19.24859766789432</v>
+        <v>13.28760285875499</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.1251730459362888</v>
+        <v>0.8334829319487406</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5666,31 +5666,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.4744961205503365</v>
+        <v>0.0114340746977891</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6906</v>
+        <v>8032</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>298.577190325238</v>
+        <v>301.7152547634907</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>82</v>
+        <v>41.8</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5701,16 +5701,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>39.51278555185927</v>
+        <v>41.29813014855965</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>17.85269472786651</v>
+        <v>19.24859766789432</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3971803849544118</v>
+        <v>0.1251730459362888</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5719,7 +5719,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-1.468828733260629</v>
+        <v>-0.4744961205503365</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5729,21 +5729,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6918</v>
+        <v>6906</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>297.0850751975527</v>
+        <v>298.577190325238</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>74.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5754,13 +5754,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>52.23885075978043</v>
+        <v>39.51278555185927</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>13.4830962017074</v>
+        <v>17.85269472786651</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4409605856337868</v>
+        <v>0.3971803849544118</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>1</v>
@@ -5772,31 +5772,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1896822961093553</v>
+        <v>-1.468828733260629</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6931</v>
+        <v>6918</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>296.6313441542502</v>
+        <v>297.0850751975527</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>39.75</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5807,13 +5807,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>40.62086957529913</v>
+        <v>52.23885075978043</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.3503840018668</v>
+        <v>13.4830962017074</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5679778257363548</v>
+        <v>0.4409605856337868</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>1</v>
@@ -5825,7 +5825,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.068982221357753</v>
+        <v>0.1896822961093553</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5835,21 +5835,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>7721</v>
+        <v>6931</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>294.8380842922334</v>
+        <v>296.6313441542502</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>71</v>
+        <v>39.75</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5860,16 +5860,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>44.80168470812589</v>
+        <v>40.62086957529913</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>10.93154352012251</v>
+        <v>17.3503840018668</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.1445584497526122</v>
+        <v>0.5679778257363548</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5878,31 +5878,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.2848709066211199</v>
+        <v>0.068982221357753</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6967</v>
+        <v>7721</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>294.6658513074201</v>
+        <v>294.8380842922334</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5913,13 +5913,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>43.2632513968686</v>
+        <v>44.80168470812589</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.28915740397964</v>
+        <v>10.93154352012251</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6501533329938837</v>
+        <v>0.1445584497526122</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5931,31 +5931,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.1277832835988867</v>
+        <v>-0.2848709066211199</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6854</v>
+        <v>6967</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>287.9321804976679</v>
+        <v>294.6658513074201</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>113.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5966,13 +5966,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>29.76518114133657</v>
+        <v>43.2632513968686</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>23.47971786607372</v>
+        <v>12.28915740397964</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.527707214277649</v>
+        <v>0.6501533329938837</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5984,11 +5984,11 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.1925840124130724</v>
+        <v>-0.1277832835988867</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -6418,21 +6418,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6908</v>
+        <v>6909</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>243.6464737414201</v>
+        <v>257.2207977387619</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>36.6</v>
+        <v>51.3</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6443,13 +6443,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>35.67848240626194</v>
+        <v>44.84173236254644</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.1613569677956</v>
+        <v>16.43522249029083</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.9148933175702304</v>
+        <v>0.2418643455155242</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6461,11 +6461,11 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.08735674367619881</v>
+        <v>-0.4028328879516456</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
@@ -6630,21 +6630,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6921</v>
+        <v>6899</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>226.6310574268157</v>
+        <v>218.6683684623978</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>68</v>
+        <v>54.7</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6655,13 +6655,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>38.93343411596706</v>
+        <v>34.04625825395961</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>17.35227948019281</v>
+        <v>14.93820479383245</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.1668720314980874</v>
+        <v>0.9242118449439766</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6673,31 +6673,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.2385507695230706</v>
+        <v>-0.3323764673576509</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6899</v>
+        <v>7749</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>218.6683684623978</v>
+        <v>216.15866189966</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>54.7</v>
+        <v>404</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6708,13 +6708,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>34.04625825395961</v>
+        <v>34.08472250739553</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>14.93820479383245</v>
+        <v>15.49490569347116</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.9242118449439766</v>
+        <v>0.2834734020563929</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6726,31 +6726,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.3323764673576509</v>
+        <v>-4.924311626850146</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6909</v>
+        <v>6885</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>217.220797738762</v>
+        <v>215.2736476833169</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>51.3</v>
+        <v>21.85</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6761,16 +6761,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>44.84173236254644</v>
+        <v>47.2964484181453</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>16.43522249029083</v>
+        <v>17.69471854733938</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.2418643455155242</v>
+        <v>0.4064297818704699</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6779,31 +6779,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.4028328879516456</v>
+        <v>0.06826108265377059</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>7749</v>
+        <v>8044</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>216.15866189966</v>
+        <v>214.1764594044797</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>404</v>
+        <v>26.8</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6814,13 +6814,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>34.08472250739553</v>
+        <v>41.52098254858291</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.49490569347116</v>
+        <v>14.18891225190132</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.2834734020563929</v>
+        <v>0.2486213192443414</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6832,31 +6832,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-4.924311626850146</v>
+        <v>-0.3977575223101354</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6885</v>
+        <v>6908</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>215.2736476833169</v>
+        <v>213.6464737414201</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>21.85</v>
+        <v>36.6</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6867,16 +6867,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>47.2964484181453</v>
+        <v>35.67848240626194</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>17.69471854733938</v>
+        <v>16.1613569677956</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.4064297818704699</v>
+        <v>0.9148933175702304</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6885,7 +6885,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.06826108265377059</v>
+        <v>-0.08735674367619881</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6895,21 +6895,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>8044</v>
+        <v>7730</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>214.1764594044797</v>
+        <v>209.1135777707526</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>26.8</v>
+        <v>183</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6920,13 +6920,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>41.52098254858291</v>
+        <v>47.84907312567253</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>14.18891225190132</v>
+        <v>10.27348699793313</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.2486213192443414</v>
+        <v>0.9215102340619056</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6938,31 +6938,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.3977575223101354</v>
+        <v>0.4485259988977426</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7730</v>
+        <v>6953</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>209.1135777707526</v>
+        <v>202.7766110895432</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6973,13 +6973,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>47.84907312567253</v>
+        <v>43.79332010999956</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>10.27348699793313</v>
+        <v>12.77746564868914</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.9215102340619056</v>
+        <v>0.3861295447556247</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6991,7 +6991,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.4485259988977426</v>
+        <v>0.2059930994131873</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7001,21 +7001,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6953</v>
+        <v>6859</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>202.7766110895432</v>
+        <v>202.4637793579379</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>228</v>
+        <v>120.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7026,13 +7026,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>43.79332010999956</v>
+        <v>42.96529548176591</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>12.77746564868914</v>
+        <v>15.9452175682549</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.3861295447556247</v>
+        <v>0.1066902570738212</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7044,31 +7044,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.2059930994131873</v>
+        <v>-1.061681770343376</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6859</v>
+        <v>6921</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>202.4637793579379</v>
+        <v>196.6310574268157</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>120.5</v>
+        <v>68</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7079,13 +7079,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>42.96529548176591</v>
+        <v>38.93343411596706</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>15.9452175682549</v>
+        <v>17.35227948019281</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.1066902570738212</v>
+        <v>0.1668720314980874</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7097,11 +7097,11 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-1.061681770343376</v>
+        <v>0.2385507695230706</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
